--- a/Залишки і доступність товарів - Мисак (XLSX) (1).xlsx
+++ b/Залишки і доступність товарів - Мисак (XLSX) (1).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t>Залишки і доступність товарів</t>
   </si>
@@ -739,12 +739,42 @@
     <t>Плитка  MJS12106-3  120*60 MATT</t>
   </si>
   <si>
+    <t>00-00022043</t>
+  </si>
+  <si>
+    <t>Плитка BULGARIA BLACK 120*60 HIGH GLOSS</t>
+  </si>
+  <si>
+    <t>00-00022056</t>
+  </si>
+  <si>
+    <t>Плитка EGANCE GREY 120*60 GLOSSY CARVING</t>
+  </si>
+  <si>
     <t>00-00021993</t>
   </si>
   <si>
     <t>Плитка EXCELLENT WHITE TG6121G 120*60 </t>
   </si>
   <si>
+    <t>00-00021894</t>
+  </si>
+  <si>
+    <t>Плитка IVORY PEAR 120*60 HIGH GLOSS</t>
+  </si>
+  <si>
+    <t>00-00022050</t>
+  </si>
+  <si>
+    <t>Плитка LABRADORITE BLUE 120*60 HIGH GLOSS</t>
+  </si>
+  <si>
+    <t>00-00022048</t>
+  </si>
+  <si>
+    <t>Плитка LABRADORITE GREEN 120*60 HIGH GLOSS</t>
+  </si>
+  <si>
     <t>00-00020662</t>
   </si>
   <si>
@@ -761,6 +791,12 @@
   </si>
   <si>
     <t>Плитка ONIX GOLD MORE KN6601 60*60</t>
+  </si>
+  <si>
+    <t>00-00022047</t>
+  </si>
+  <si>
+    <t>Плитка TIGER ONIX 120*60 HIGH GLOSS</t>
   </si>
   <si>
     <t>00-00021800</t>
@@ -1013,7 +1049,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="Q364"/>
+  <dimension ref="Q370"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="true"/>
@@ -3517,17 +3553,17 @@
       </c>
       <c r="K76" s="11" t="e"/>
       <c r="L76" s="10" t="n">
-        <v>18.72</v>
+        <v>17.28</v>
       </c>
       <c r="M76" s="10" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="N76" s="11" t="e"/>
       <c r="O76" s="10" t="n">
-        <v>18.72</v>
+        <v>17.28</v>
       </c>
       <c r="P76" s="10" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="Q76" s="12" t="e"/>
     </row>
@@ -7023,19 +7059,21 @@
       <c r="J180" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="K180" s="11" t="e"/>
+      <c r="K180" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="L180" s="10" t="n">
         <v>3</v>
       </c>
       <c r="M180" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N180" s="11" t="e"/>
       <c r="O180" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P180" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q180" s="12" t="e"/>
     </row>
@@ -7611,7 +7649,7 @@
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="1">
       <c r="A197" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B197" s="7" t="e"/>
       <c r="C197" s="7" t="e"/>
@@ -7620,33 +7658,33 @@
       </c>
       <c r="E197" s="8" t="e"/>
       <c r="F197" s="9" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="G197" s="9" t="e"/>
       <c r="H197" s="9" t="s">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="I197" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J197" s="19" t="n">
-        <v>1094.4</v>
-      </c>
+      <c r="J197" s="11" t="e"/>
       <c r="K197" s="11" t="e"/>
       <c r="L197" s="11" t="e"/>
-      <c r="M197" s="19" t="n">
-        <v>1094.4</v>
-      </c>
-      <c r="N197" s="11" t="e"/>
+      <c r="M197" s="11" t="e"/>
+      <c r="N197" s="10" t="n">
+        <v>489.6</v>
+      </c>
       <c r="O197" s="11" t="e"/>
-      <c r="P197" s="19" t="n">
-        <v>1094.4</v>
-      </c>
-      <c r="Q197" s="12" t="e"/>
+      <c r="P197" s="10" t="n">
+        <v>489.6</v>
+      </c>
+      <c r="Q197" s="10" t="n">
+        <v>489.6</v>
+      </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="1">
       <c r="A198" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B198" s="7" t="e"/>
       <c r="C198" s="7" t="e"/>
@@ -7655,37 +7693,33 @@
       </c>
       <c r="E198" s="8" t="e"/>
       <c r="F198" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G198" s="9" t="e"/>
       <c r="H198" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I198" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J198" s="10" t="n">
-        <v>95.4</v>
+      <c r="J198" s="19" t="n">
+        <v>1094.4</v>
       </c>
       <c r="K198" s="11" t="e"/>
-      <c r="L198" s="10" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="M198" s="10" t="n">
-        <v>71.28</v>
+      <c r="L198" s="11" t="e"/>
+      <c r="M198" s="19" t="n">
+        <v>1094.4</v>
       </c>
       <c r="N198" s="11" t="e"/>
-      <c r="O198" s="10" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="P198" s="10" t="n">
-        <v>71.28</v>
+      <c r="O198" s="11" t="e"/>
+      <c r="P198" s="19" t="n">
+        <v>1094.4</v>
       </c>
       <c r="Q198" s="12" t="e"/>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="1">
       <c r="A199" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B199" s="7" t="e"/>
       <c r="C199" s="7" t="e"/>
@@ -7694,27 +7728,31 @@
       </c>
       <c r="E199" s="8" t="e"/>
       <c r="F199" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G199" s="9" t="e"/>
       <c r="H199" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I199" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J199" s="10" t="n">
-        <v>535.68</v>
+        <v>95.4</v>
       </c>
       <c r="K199" s="11" t="e"/>
-      <c r="L199" s="11" t="e"/>
+      <c r="L199" s="10" t="n">
+        <v>24.12</v>
+      </c>
       <c r="M199" s="10" t="n">
-        <v>535.68</v>
+        <v>71.28</v>
       </c>
       <c r="N199" s="11" t="e"/>
-      <c r="O199" s="11" t="e"/>
+      <c r="O199" s="10" t="n">
+        <v>24.12</v>
+      </c>
       <c r="P199" s="10" t="n">
-        <v>535.68</v>
+        <v>71.28</v>
       </c>
       <c r="Q199" s="12" t="e"/>
     </row>
@@ -7729,33 +7767,33 @@
       </c>
       <c r="E200" s="8" t="e"/>
       <c r="F200" s="9" t="s">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="G200" s="9" t="e"/>
       <c r="H200" s="9" t="s">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="I200" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J200" s="11" t="e"/>
+      <c r="J200" s="10" t="n">
+        <v>535.68</v>
+      </c>
       <c r="K200" s="11" t="e"/>
       <c r="L200" s="11" t="e"/>
-      <c r="M200" s="11" t="e"/>
-      <c r="N200" s="10" t="n">
-        <v>754.56</v>
-      </c>
+      <c r="M200" s="10" t="n">
+        <v>535.68</v>
+      </c>
+      <c r="N200" s="11" t="e"/>
       <c r="O200" s="11" t="e"/>
       <c r="P200" s="10" t="n">
-        <v>754.56</v>
-      </c>
-      <c r="Q200" s="10" t="n">
-        <v>754.56</v>
-      </c>
+        <v>535.68</v>
+      </c>
+      <c r="Q200" s="12" t="e"/>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="1">
       <c r="A201" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B201" s="7" t="e"/>
       <c r="C201" s="7" t="e"/>
@@ -7764,33 +7802,33 @@
       </c>
       <c r="E201" s="8" t="e"/>
       <c r="F201" s="9" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="G201" s="9" t="e"/>
       <c r="H201" s="9" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="I201" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J201" s="10" t="n">
-        <v>4.32</v>
-      </c>
+      <c r="J201" s="11" t="e"/>
       <c r="K201" s="11" t="e"/>
       <c r="L201" s="11" t="e"/>
-      <c r="M201" s="10" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N201" s="11" t="e"/>
+      <c r="M201" s="11" t="e"/>
+      <c r="N201" s="10" t="n">
+        <v>391.68</v>
+      </c>
       <c r="O201" s="11" t="e"/>
       <c r="P201" s="10" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Q201" s="12" t="e"/>
+        <v>391.68</v>
+      </c>
+      <c r="Q201" s="10" t="n">
+        <v>391.68</v>
+      </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="1">
       <c r="A202" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B202" s="7" t="e"/>
       <c r="C202" s="7" t="e"/>
@@ -7799,29 +7837,29 @@
       </c>
       <c r="E202" s="8" t="e"/>
       <c r="F202" s="9" t="s">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="G202" s="9" t="e"/>
       <c r="H202" s="9" t="s">
-        <v>85</v>
+        <v>246</v>
       </c>
       <c r="I202" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J202" s="10" t="n">
-        <v>317.52</v>
-      </c>
+      <c r="J202" s="11" t="e"/>
       <c r="K202" s="11" t="e"/>
       <c r="L202" s="11" t="e"/>
-      <c r="M202" s="10" t="n">
-        <v>317.52</v>
-      </c>
-      <c r="N202" s="11" t="e"/>
+      <c r="M202" s="11" t="e"/>
+      <c r="N202" s="10" t="n">
+        <v>754.56</v>
+      </c>
       <c r="O202" s="11" t="e"/>
       <c r="P202" s="10" t="n">
-        <v>317.52</v>
-      </c>
-      <c r="Q202" s="12" t="e"/>
+        <v>754.56</v>
+      </c>
+      <c r="Q202" s="10" t="n">
+        <v>754.56</v>
+      </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="1">
       <c r="A203" s="7" t="n">
@@ -7834,33 +7872,33 @@
       </c>
       <c r="E203" s="8" t="e"/>
       <c r="F203" s="9" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="G203" s="9" t="e"/>
       <c r="H203" s="9" t="s">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="I203" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J203" s="10" t="n">
-        <v>150.48</v>
+        <v>4.32</v>
       </c>
       <c r="K203" s="11" t="e"/>
       <c r="L203" s="11" t="e"/>
       <c r="M203" s="10" t="n">
-        <v>150.48</v>
+        <v>4.32</v>
       </c>
       <c r="N203" s="11" t="e"/>
       <c r="O203" s="11" t="e"/>
       <c r="P203" s="10" t="n">
-        <v>150.48</v>
+        <v>4.32</v>
       </c>
       <c r="Q203" s="12" t="e"/>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="1">
       <c r="A204" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B204" s="7" t="e"/>
       <c r="C204" s="7" t="e"/>
@@ -7869,31 +7907,27 @@
       </c>
       <c r="E204" s="8" t="e"/>
       <c r="F204" s="9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G204" s="9" t="e"/>
       <c r="H204" s="9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I204" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J204" s="10" t="n">
-        <v>569.52</v>
+        <v>317.52</v>
       </c>
       <c r="K204" s="11" t="e"/>
-      <c r="L204" s="10" t="n">
-        <v>2.16</v>
-      </c>
+      <c r="L204" s="11" t="e"/>
       <c r="M204" s="10" t="n">
-        <v>567.36</v>
+        <v>317.52</v>
       </c>
       <c r="N204" s="11" t="e"/>
-      <c r="O204" s="10" t="n">
-        <v>2.16</v>
-      </c>
+      <c r="O204" s="11" t="e"/>
       <c r="P204" s="10" t="n">
-        <v>567.36</v>
+        <v>317.52</v>
       </c>
       <c r="Q204" s="12" t="e"/>
     </row>
@@ -7908,29 +7942,29 @@
       </c>
       <c r="E205" s="8" t="e"/>
       <c r="F205" s="9" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G205" s="9" t="e"/>
       <c r="H205" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I205" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J205" s="11" t="e"/>
+      <c r="J205" s="10" t="n">
+        <v>150.48</v>
+      </c>
       <c r="K205" s="11" t="e"/>
       <c r="L205" s="11" t="e"/>
-      <c r="M205" s="11" t="e"/>
-      <c r="N205" s="10" t="n">
-        <v>312.48</v>
-      </c>
+      <c r="M205" s="10" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="N205" s="11" t="e"/>
       <c r="O205" s="11" t="e"/>
       <c r="P205" s="10" t="n">
-        <v>312.48</v>
-      </c>
-      <c r="Q205" s="10" t="n">
-        <v>312.48</v>
-      </c>
+        <v>150.48</v>
+      </c>
+      <c r="Q205" s="12" t="e"/>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="1">
       <c r="A206" s="7" t="n">
@@ -7943,27 +7977,31 @@
       </c>
       <c r="E206" s="8" t="e"/>
       <c r="F206" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G206" s="9" t="e"/>
       <c r="H206" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I206" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J206" s="10" t="n">
+        <v>569.52</v>
+      </c>
+      <c r="K206" s="11" t="e"/>
+      <c r="L206" s="10" t="n">
         <v>2.16</v>
       </c>
-      <c r="K206" s="11" t="e"/>
-      <c r="L206" s="11" t="e"/>
       <c r="M206" s="10" t="n">
+        <v>567.36</v>
+      </c>
+      <c r="N206" s="11" t="e"/>
+      <c r="O206" s="10" t="n">
         <v>2.16</v>
       </c>
-      <c r="N206" s="11" t="e"/>
-      <c r="O206" s="11" t="e"/>
       <c r="P206" s="10" t="n">
-        <v>2.16</v>
+        <v>567.36</v>
       </c>
       <c r="Q206" s="12" t="e"/>
     </row>
@@ -7974,37 +8012,37 @@
       <c r="B207" s="7" t="e"/>
       <c r="C207" s="7" t="e"/>
       <c r="D207" s="8" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="E207" s="8" t="e"/>
       <c r="F207" s="9" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G207" s="9" t="e"/>
       <c r="H207" s="9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I207" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J207" s="10" t="n">
-        <v>1.125</v>
-      </c>
+      <c r="J207" s="11" t="e"/>
       <c r="K207" s="11" t="e"/>
       <c r="L207" s="11" t="e"/>
-      <c r="M207" s="10" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="N207" s="11" t="e"/>
+      <c r="M207" s="11" t="e"/>
+      <c r="N207" s="10" t="n">
+        <v>440.64</v>
+      </c>
       <c r="O207" s="11" t="e"/>
       <c r="P207" s="10" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="Q207" s="12" t="e"/>
+        <v>440.64</v>
+      </c>
+      <c r="Q207" s="10" t="n">
+        <v>440.64</v>
+      </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="1">
       <c r="A208" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B208" s="7" t="e"/>
       <c r="C208" s="7" t="e"/>
@@ -8013,33 +8051,33 @@
       </c>
       <c r="E208" s="8" t="e"/>
       <c r="F208" s="9" t="s">
-        <v>96</v>
+        <v>249</v>
       </c>
       <c r="G208" s="9" t="e"/>
       <c r="H208" s="9" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="I208" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J208" s="10" t="n">
-        <v>289.44</v>
-      </c>
+      <c r="J208" s="11" t="e"/>
       <c r="K208" s="11" t="e"/>
       <c r="L208" s="11" t="e"/>
-      <c r="M208" s="10" t="n">
-        <v>289.44</v>
-      </c>
-      <c r="N208" s="11" t="e"/>
+      <c r="M208" s="11" t="e"/>
+      <c r="N208" s="10" t="n">
+        <v>489.6</v>
+      </c>
       <c r="O208" s="11" t="e"/>
       <c r="P208" s="10" t="n">
-        <v>289.44</v>
-      </c>
-      <c r="Q208" s="12" t="e"/>
+        <v>489.6</v>
+      </c>
+      <c r="Q208" s="10" t="n">
+        <v>489.6</v>
+      </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="1">
       <c r="A209" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B209" s="7" t="e"/>
       <c r="C209" s="7" t="e"/>
@@ -8048,33 +8086,33 @@
       </c>
       <c r="E209" s="8" t="e"/>
       <c r="F209" s="9" t="s">
-        <v>98</v>
+        <v>251</v>
       </c>
       <c r="G209" s="9" t="e"/>
       <c r="H209" s="9" t="s">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="I209" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J209" s="10" t="n">
-        <v>607.68</v>
-      </c>
+      <c r="J209" s="11" t="e"/>
       <c r="K209" s="11" t="e"/>
       <c r="L209" s="11" t="e"/>
-      <c r="M209" s="10" t="n">
-        <v>607.68</v>
-      </c>
-      <c r="N209" s="11" t="e"/>
+      <c r="M209" s="11" t="e"/>
+      <c r="N209" s="10" t="n">
+        <v>538.56</v>
+      </c>
       <c r="O209" s="11" t="e"/>
       <c r="P209" s="10" t="n">
-        <v>607.68</v>
-      </c>
-      <c r="Q209" s="12" t="e"/>
+        <v>538.56</v>
+      </c>
+      <c r="Q209" s="10" t="n">
+        <v>538.56</v>
+      </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="1">
       <c r="A210" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B210" s="7" t="e"/>
       <c r="C210" s="7" t="e"/>
@@ -8083,33 +8121,33 @@
       </c>
       <c r="E210" s="8" t="e"/>
       <c r="F210" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G210" s="9" t="e"/>
       <c r="H210" s="9" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I210" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J210" s="10" t="n">
-        <v>151.92</v>
-      </c>
+      <c r="J210" s="11" t="e"/>
       <c r="K210" s="11" t="e"/>
       <c r="L210" s="11" t="e"/>
-      <c r="M210" s="10" t="n">
-        <v>151.92</v>
-      </c>
-      <c r="N210" s="11" t="e"/>
+      <c r="M210" s="11" t="e"/>
+      <c r="N210" s="10" t="n">
+        <v>312.48</v>
+      </c>
       <c r="O210" s="11" t="e"/>
       <c r="P210" s="10" t="n">
-        <v>151.92</v>
-      </c>
-      <c r="Q210" s="12" t="e"/>
+        <v>312.48</v>
+      </c>
+      <c r="Q210" s="10" t="n">
+        <v>312.48</v>
+      </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="1">
       <c r="A211" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B211" s="7" t="e"/>
       <c r="C211" s="7" t="e"/>
@@ -8118,27 +8156,27 @@
       </c>
       <c r="E211" s="8" t="e"/>
       <c r="F211" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G211" s="9" t="e"/>
       <c r="H211" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I211" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J211" s="10" t="n">
-        <v>10.44</v>
+        <v>2.16</v>
       </c>
       <c r="K211" s="11" t="e"/>
       <c r="L211" s="11" t="e"/>
       <c r="M211" s="10" t="n">
-        <v>10.44</v>
+        <v>2.16</v>
       </c>
       <c r="N211" s="11" t="e"/>
       <c r="O211" s="11" t="e"/>
       <c r="P211" s="10" t="n">
-        <v>10.44</v>
+        <v>2.16</v>
       </c>
       <c r="Q211" s="12" t="e"/>
     </row>
@@ -8149,41 +8187,37 @@
       <c r="B212" s="7" t="e"/>
       <c r="C212" s="7" t="e"/>
       <c r="D212" s="8" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="E212" s="8" t="e"/>
       <c r="F212" s="9" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="G212" s="9" t="e"/>
       <c r="H212" s="9" t="s">
-        <v>105</v>
+        <v>254</v>
       </c>
       <c r="I212" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J212" s="10" t="n">
-        <v>369.36</v>
+        <v>1.125</v>
       </c>
       <c r="K212" s="11" t="e"/>
-      <c r="L212" s="10" t="n">
-        <v>17.28</v>
-      </c>
+      <c r="L212" s="11" t="e"/>
       <c r="M212" s="10" t="n">
-        <v>352.08</v>
+        <v>1.125</v>
       </c>
       <c r="N212" s="11" t="e"/>
-      <c r="O212" s="10" t="n">
-        <v>17.28</v>
-      </c>
+      <c r="O212" s="11" t="e"/>
       <c r="P212" s="10" t="n">
-        <v>352.08</v>
+        <v>1.125</v>
       </c>
       <c r="Q212" s="12" t="e"/>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="1">
       <c r="A213" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B213" s="7" t="e"/>
       <c r="C213" s="7" t="e"/>
@@ -8192,29 +8226,29 @@
       </c>
       <c r="E213" s="8" t="e"/>
       <c r="F213" s="9" t="s">
-        <v>245</v>
+        <v>96</v>
       </c>
       <c r="G213" s="9" t="e"/>
       <c r="H213" s="9" t="s">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="I213" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J213" s="11" t="e"/>
+      <c r="J213" s="10" t="n">
+        <v>289.44</v>
+      </c>
       <c r="K213" s="11" t="e"/>
       <c r="L213" s="11" t="e"/>
-      <c r="M213" s="11" t="e"/>
-      <c r="N213" s="10" t="n">
-        <v>766.08</v>
-      </c>
+      <c r="M213" s="10" t="n">
+        <v>289.44</v>
+      </c>
+      <c r="N213" s="11" t="e"/>
       <c r="O213" s="11" t="e"/>
       <c r="P213" s="10" t="n">
-        <v>766.08</v>
-      </c>
-      <c r="Q213" s="10" t="n">
-        <v>766.08</v>
-      </c>
+        <v>289.44</v>
+      </c>
+      <c r="Q213" s="12" t="e"/>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="1">
       <c r="A214" s="7" t="n">
@@ -8227,33 +8261,33 @@
       </c>
       <c r="E214" s="8" t="e"/>
       <c r="F214" s="9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G214" s="9" t="e"/>
       <c r="H214" s="9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I214" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J214" s="10" t="n">
-        <v>66.96</v>
+        <v>607.68</v>
       </c>
       <c r="K214" s="11" t="e"/>
       <c r="L214" s="11" t="e"/>
       <c r="M214" s="10" t="n">
-        <v>66.96</v>
+        <v>607.68</v>
       </c>
       <c r="N214" s="11" t="e"/>
       <c r="O214" s="11" t="e"/>
       <c r="P214" s="10" t="n">
-        <v>66.96</v>
+        <v>607.68</v>
       </c>
       <c r="Q214" s="12" t="e"/>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="1">
       <c r="A215" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B215" s="7" t="e"/>
       <c r="C215" s="7" t="e"/>
@@ -8262,33 +8296,33 @@
       </c>
       <c r="E215" s="8" t="e"/>
       <c r="F215" s="9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G215" s="9" t="e"/>
       <c r="H215" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I215" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J215" s="10" t="n">
-        <v>77.76</v>
+        <v>151.92</v>
       </c>
       <c r="K215" s="11" t="e"/>
       <c r="L215" s="11" t="e"/>
       <c r="M215" s="10" t="n">
-        <v>77.76</v>
+        <v>151.92</v>
       </c>
       <c r="N215" s="11" t="e"/>
       <c r="O215" s="11" t="e"/>
       <c r="P215" s="10" t="n">
-        <v>77.76</v>
+        <v>151.92</v>
       </c>
       <c r="Q215" s="12" t="e"/>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="1">
       <c r="A216" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B216" s="7" t="e"/>
       <c r="C216" s="7" t="e"/>
@@ -8297,27 +8331,27 @@
       </c>
       <c r="E216" s="8" t="e"/>
       <c r="F216" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G216" s="9" t="e"/>
       <c r="H216" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I216" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J216" s="10" t="n">
-        <v>33.12</v>
+        <v>10.44</v>
       </c>
       <c r="K216" s="11" t="e"/>
       <c r="L216" s="11" t="e"/>
       <c r="M216" s="10" t="n">
-        <v>33.12</v>
+        <v>10.44</v>
       </c>
       <c r="N216" s="11" t="e"/>
       <c r="O216" s="11" t="e"/>
       <c r="P216" s="10" t="n">
-        <v>33.12</v>
+        <v>10.44</v>
       </c>
       <c r="Q216" s="12" t="e"/>
     </row>
@@ -8332,33 +8366,37 @@
       </c>
       <c r="E217" s="8" t="e"/>
       <c r="F217" s="9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G217" s="9" t="e"/>
       <c r="H217" s="9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I217" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J217" s="10" t="n">
-        <v>102.24</v>
+        <v>369.36</v>
       </c>
       <c r="K217" s="11" t="e"/>
-      <c r="L217" s="11" t="e"/>
+      <c r="L217" s="10" t="n">
+        <v>17.28</v>
+      </c>
       <c r="M217" s="10" t="n">
-        <v>102.24</v>
+        <v>352.08</v>
       </c>
       <c r="N217" s="11" t="e"/>
-      <c r="O217" s="11" t="e"/>
+      <c r="O217" s="10" t="n">
+        <v>17.28</v>
+      </c>
       <c r="P217" s="10" t="n">
-        <v>102.24</v>
+        <v>352.08</v>
       </c>
       <c r="Q217" s="12" t="e"/>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="1">
       <c r="A218" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B218" s="7" t="e"/>
       <c r="C218" s="7" t="e"/>
@@ -8367,29 +8405,29 @@
       </c>
       <c r="E218" s="8" t="e"/>
       <c r="F218" s="9" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="G218" s="9" t="e"/>
       <c r="H218" s="9" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="I218" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J218" s="10" t="n">
-        <v>2.16</v>
-      </c>
+      <c r="J218" s="11" t="e"/>
       <c r="K218" s="11" t="e"/>
       <c r="L218" s="11" t="e"/>
-      <c r="M218" s="10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="N218" s="11" t="e"/>
+      <c r="M218" s="11" t="e"/>
+      <c r="N218" s="10" t="n">
+        <v>766.08</v>
+      </c>
       <c r="O218" s="11" t="e"/>
       <c r="P218" s="10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q218" s="12" t="e"/>
+        <v>766.08</v>
+      </c>
+      <c r="Q218" s="10" t="n">
+        <v>766.08</v>
+      </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="1">
       <c r="A219" s="7" t="n">
@@ -8402,33 +8440,33 @@
       </c>
       <c r="E219" s="8" t="e"/>
       <c r="F219" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G219" s="9" t="e"/>
       <c r="H219" s="9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I219" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J219" s="10" t="n">
-        <v>315.36</v>
+        <v>66.96</v>
       </c>
       <c r="K219" s="11" t="e"/>
       <c r="L219" s="11" t="e"/>
       <c r="M219" s="10" t="n">
-        <v>315.36</v>
+        <v>66.96</v>
       </c>
       <c r="N219" s="11" t="e"/>
       <c r="O219" s="11" t="e"/>
       <c r="P219" s="10" t="n">
-        <v>315.36</v>
+        <v>66.96</v>
       </c>
       <c r="Q219" s="12" t="e"/>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="1">
       <c r="A220" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B220" s="7" t="e"/>
       <c r="C220" s="7" t="e"/>
@@ -8437,41 +8475,33 @@
       </c>
       <c r="E220" s="8" t="e"/>
       <c r="F220" s="9" t="s">
-        <v>247</v>
+        <v>108</v>
       </c>
       <c r="G220" s="9" t="e"/>
       <c r="H220" s="9" t="s">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="I220" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J220" s="10" t="n">
-        <v>48.6</v>
+        <v>77.76</v>
       </c>
       <c r="K220" s="11" t="e"/>
-      <c r="L220" s="10" t="n">
-        <v>32.4</v>
-      </c>
+      <c r="L220" s="11" t="e"/>
       <c r="M220" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N220" s="10" t="n">
-        <v>731.52</v>
-      </c>
-      <c r="O220" s="10" t="n">
-        <v>56.88</v>
-      </c>
+        <v>77.76</v>
+      </c>
+      <c r="N220" s="11" t="e"/>
+      <c r="O220" s="11" t="e"/>
       <c r="P220" s="10" t="n">
-        <v>723.24</v>
-      </c>
-      <c r="Q220" s="10" t="n">
-        <v>723.24</v>
-      </c>
+        <v>77.76</v>
+      </c>
+      <c r="Q220" s="12" t="e"/>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="1">
       <c r="A221" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B221" s="7" t="e"/>
       <c r="C221" s="7" t="e"/>
@@ -8480,31 +8510,27 @@
       </c>
       <c r="E221" s="8" t="e"/>
       <c r="F221" s="9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G221" s="9" t="e"/>
       <c r="H221" s="9" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I221" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>140.4</v>
+        <v>33.12</v>
       </c>
       <c r="K221" s="11" t="e"/>
-      <c r="L221" s="10" t="n">
-        <v>91.44</v>
-      </c>
+      <c r="L221" s="11" t="e"/>
       <c r="M221" s="10" t="n">
-        <v>48.96</v>
+        <v>33.12</v>
       </c>
       <c r="N221" s="11" t="e"/>
-      <c r="O221" s="10" t="n">
-        <v>91.44</v>
-      </c>
+      <c r="O221" s="11" t="e"/>
       <c r="P221" s="10" t="n">
-        <v>48.96</v>
+        <v>33.12</v>
       </c>
       <c r="Q221" s="12" t="e"/>
     </row>
@@ -8519,37 +8545,33 @@
       </c>
       <c r="E222" s="8" t="e"/>
       <c r="F222" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G222" s="9" t="e"/>
       <c r="H222" s="9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I222" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J222" s="10" t="n">
-        <v>6.48</v>
+        <v>102.24</v>
       </c>
       <c r="K222" s="11" t="e"/>
       <c r="L222" s="11" t="e"/>
       <c r="M222" s="10" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="N222" s="10" t="n">
-        <v>607.68</v>
-      </c>
+        <v>102.24</v>
+      </c>
+      <c r="N222" s="11" t="e"/>
       <c r="O222" s="11" t="e"/>
       <c r="P222" s="10" t="n">
-        <v>614.16</v>
-      </c>
-      <c r="Q222" s="10" t="n">
-        <v>614.16</v>
-      </c>
+        <v>102.24</v>
+      </c>
+      <c r="Q222" s="12" t="e"/>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="1">
       <c r="A223" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B223" s="7" t="e"/>
       <c r="C223" s="7" t="e"/>
@@ -8558,27 +8580,27 @@
       </c>
       <c r="E223" s="8" t="e"/>
       <c r="F223" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G223" s="9" t="e"/>
       <c r="H223" s="9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I223" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>9.36</v>
+        <v>2.16</v>
       </c>
       <c r="K223" s="11" t="e"/>
       <c r="L223" s="11" t="e"/>
       <c r="M223" s="10" t="n">
-        <v>9.36</v>
+        <v>2.16</v>
       </c>
       <c r="N223" s="11" t="e"/>
       <c r="O223" s="11" t="e"/>
       <c r="P223" s="10" t="n">
-        <v>9.36</v>
+        <v>2.16</v>
       </c>
       <c r="Q223" s="12" t="e"/>
     </row>
@@ -8593,39 +8615,33 @@
       </c>
       <c r="E224" s="8" t="e"/>
       <c r="F224" s="9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G224" s="9" t="e"/>
       <c r="H224" s="9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I224" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J224" s="10" t="n">
-        <v>640.08</v>
-      </c>
-      <c r="K224" s="10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L224" s="10" t="n">
-        <v>165.6</v>
-      </c>
+        <v>315.36</v>
+      </c>
+      <c r="K224" s="11" t="e"/>
+      <c r="L224" s="11" t="e"/>
       <c r="M224" s="10" t="n">
-        <v>472.32</v>
+        <v>315.36</v>
       </c>
       <c r="N224" s="11" t="e"/>
-      <c r="O224" s="10" t="n">
-        <v>167.76</v>
-      </c>
+      <c r="O224" s="11" t="e"/>
       <c r="P224" s="10" t="n">
-        <v>472.32</v>
+        <v>315.36</v>
       </c>
       <c r="Q224" s="12" t="e"/>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="1">
       <c r="A225" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B225" s="7" t="e"/>
       <c r="C225" s="7" t="e"/>
@@ -8634,70 +8650,74 @@
       </c>
       <c r="E225" s="8" t="e"/>
       <c r="F225" s="9" t="s">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="G225" s="9" t="e"/>
       <c r="H225" s="9" t="s">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="I225" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J225" s="10" t="n">
-        <v>87.12</v>
-      </c>
-      <c r="K225" s="10" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="L225" s="11" t="e"/>
+        <v>48.6</v>
+      </c>
+      <c r="K225" s="11" t="e"/>
+      <c r="L225" s="10" t="n">
+        <v>32.4</v>
+      </c>
       <c r="M225" s="10" t="n">
-        <v>79.2</v>
+        <v>16.2</v>
       </c>
       <c r="N225" s="10" t="n">
-        <v>679.68</v>
+        <v>731.52</v>
       </c>
       <c r="O225" s="10" t="n">
-        <v>7.92</v>
+        <v>56.88</v>
       </c>
       <c r="P225" s="10" t="n">
-        <v>758.88</v>
+        <v>723.24</v>
       </c>
       <c r="Q225" s="10" t="n">
-        <v>758.88</v>
+        <v>723.24</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="1">
       <c r="A226" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B226" s="7" t="e"/>
       <c r="C226" s="7" t="e"/>
       <c r="D226" s="8" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="E226" s="8" t="e"/>
       <c r="F226" s="9" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G226" s="9" t="e"/>
       <c r="H226" s="9" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I226" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J226" s="10" t="n">
-        <v>159.75</v>
+        <v>140.4</v>
       </c>
       <c r="K226" s="11" t="e"/>
-      <c r="L226" s="11" t="e"/>
+      <c r="L226" s="10" t="n">
+        <v>91.44</v>
+      </c>
       <c r="M226" s="10" t="n">
-        <v>159.75</v>
+        <v>48.96</v>
       </c>
       <c r="N226" s="11" t="e"/>
-      <c r="O226" s="11" t="e"/>
+      <c r="O226" s="10" t="n">
+        <v>91.44</v>
+      </c>
       <c r="P226" s="10" t="n">
-        <v>159.75</v>
+        <v>48.96</v>
       </c>
       <c r="Q226" s="12" t="e"/>
     </row>
@@ -8712,33 +8732,37 @@
       </c>
       <c r="E227" s="8" t="e"/>
       <c r="F227" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="G227" s="9" t="e"/>
       <c r="H227" s="9" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I227" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J227" s="10" t="n">
-        <v>222.48</v>
+        <v>6.48</v>
       </c>
       <c r="K227" s="11" t="e"/>
       <c r="L227" s="11" t="e"/>
       <c r="M227" s="10" t="n">
-        <v>222.48</v>
-      </c>
-      <c r="N227" s="11" t="e"/>
+        <v>6.48</v>
+      </c>
+      <c r="N227" s="10" t="n">
+        <v>607.68</v>
+      </c>
       <c r="O227" s="11" t="e"/>
       <c r="P227" s="10" t="n">
-        <v>222.48</v>
-      </c>
-      <c r="Q227" s="12" t="e"/>
+        <v>614.16</v>
+      </c>
+      <c r="Q227" s="10" t="n">
+        <v>614.16</v>
+      </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="1">
       <c r="A228" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B228" s="7" t="e"/>
       <c r="C228" s="7" t="e"/>
@@ -8747,27 +8771,27 @@
       </c>
       <c r="E228" s="8" t="e"/>
       <c r="F228" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="G228" s="9" t="e"/>
       <c r="H228" s="9" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="I228" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J228" s="10" t="n">
-        <v>145.44</v>
+        <v>9.36</v>
       </c>
       <c r="K228" s="11" t="e"/>
       <c r="L228" s="11" t="e"/>
       <c r="M228" s="10" t="n">
-        <v>145.44</v>
+        <v>9.36</v>
       </c>
       <c r="N228" s="11" t="e"/>
       <c r="O228" s="11" t="e"/>
       <c r="P228" s="10" t="n">
-        <v>145.44</v>
+        <v>9.36</v>
       </c>
       <c r="Q228" s="12" t="e"/>
     </row>
@@ -8782,33 +8806,35 @@
       </c>
       <c r="E229" s="8" t="e"/>
       <c r="F229" s="9" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="G229" s="9" t="e"/>
       <c r="H229" s="9" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I229" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J229" s="10" t="n">
-        <v>182.88</v>
-      </c>
-      <c r="K229" s="11" t="e"/>
-      <c r="L229" s="11" t="e"/>
+        <v>640.08</v>
+      </c>
+      <c r="K229" s="10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L229" s="10" t="n">
+        <v>165.6</v>
+      </c>
       <c r="M229" s="10" t="n">
-        <v>182.88</v>
-      </c>
-      <c r="N229" s="10" t="n">
-        <v>738.72</v>
-      </c>
-      <c r="O229" s="11" t="e"/>
+        <v>472.32</v>
+      </c>
+      <c r="N229" s="11" t="e"/>
+      <c r="O229" s="10" t="n">
+        <v>167.76</v>
+      </c>
       <c r="P229" s="10" t="n">
-        <v>921.6</v>
-      </c>
-      <c r="Q229" s="10" t="n">
-        <v>921.6</v>
-      </c>
+        <v>472.32</v>
+      </c>
+      <c r="Q229" s="12" t="e"/>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="1">
       <c r="A230" s="7" t="n">
@@ -8821,29 +8847,37 @@
       </c>
       <c r="E230" s="8" t="e"/>
       <c r="F230" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G230" s="9" t="e"/>
       <c r="H230" s="9" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I230" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J230" s="10" t="n">
-        <v>738.72</v>
-      </c>
-      <c r="K230" s="11" t="e"/>
+        <v>87.12</v>
+      </c>
+      <c r="K230" s="10" t="n">
+        <v>7.92</v>
+      </c>
       <c r="L230" s="11" t="e"/>
       <c r="M230" s="10" t="n">
-        <v>738.72</v>
-      </c>
-      <c r="N230" s="11" t="e"/>
-      <c r="O230" s="11" t="e"/>
+        <v>79.2</v>
+      </c>
+      <c r="N230" s="10" t="n">
+        <v>679.68</v>
+      </c>
+      <c r="O230" s="10" t="n">
+        <v>7.92</v>
+      </c>
       <c r="P230" s="10" t="n">
-        <v>738.72</v>
-      </c>
-      <c r="Q230" s="12" t="e"/>
+        <v>758.88</v>
+      </c>
+      <c r="Q230" s="10" t="n">
+        <v>758.88</v>
+      </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="1">
       <c r="A231" s="7" t="n">
@@ -8852,37 +8886,33 @@
       <c r="B231" s="7" t="e"/>
       <c r="C231" s="7" t="e"/>
       <c r="D231" s="8" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="E231" s="8" t="e"/>
       <c r="F231" s="9" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="G231" s="9" t="e"/>
       <c r="H231" s="9" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I231" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J231" s="10" t="n">
-        <v>45.36</v>
+        <v>159.75</v>
       </c>
       <c r="K231" s="11" t="e"/>
       <c r="L231" s="11" t="e"/>
       <c r="M231" s="10" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="N231" s="10" t="n">
-        <v>538.56</v>
-      </c>
+        <v>159.75</v>
+      </c>
+      <c r="N231" s="11" t="e"/>
       <c r="O231" s="11" t="e"/>
       <c r="P231" s="10" t="n">
-        <v>583.92</v>
-      </c>
-      <c r="Q231" s="10" t="n">
-        <v>583.92</v>
-      </c>
+        <v>159.75</v>
+      </c>
+      <c r="Q231" s="12" t="e"/>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="1">
       <c r="A232" s="7" t="n">
@@ -8895,33 +8925,33 @@
       </c>
       <c r="E232" s="8" t="e"/>
       <c r="F232" s="9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G232" s="9" t="e"/>
       <c r="H232" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I232" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J232" s="10" t="n">
-        <v>457.2</v>
+        <v>222.48</v>
       </c>
       <c r="K232" s="11" t="e"/>
       <c r="L232" s="11" t="e"/>
       <c r="M232" s="10" t="n">
-        <v>457.2</v>
+        <v>222.48</v>
       </c>
       <c r="N232" s="11" t="e"/>
       <c r="O232" s="11" t="e"/>
       <c r="P232" s="10" t="n">
-        <v>457.2</v>
+        <v>222.48</v>
       </c>
       <c r="Q232" s="12" t="e"/>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="1">
       <c r="A233" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B233" s="7" t="e"/>
       <c r="C233" s="7" t="e"/>
@@ -8930,31 +8960,27 @@
       </c>
       <c r="E233" s="8" t="e"/>
       <c r="F233" s="9" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G233" s="9" t="e"/>
       <c r="H233" s="9" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I233" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J233" s="10" t="n">
-        <v>153.36</v>
+        <v>145.44</v>
       </c>
       <c r="K233" s="11" t="e"/>
-      <c r="L233" s="10" t="n">
-        <v>38.88</v>
-      </c>
+      <c r="L233" s="11" t="e"/>
       <c r="M233" s="10" t="n">
-        <v>114.48</v>
+        <v>145.44</v>
       </c>
       <c r="N233" s="11" t="e"/>
-      <c r="O233" s="10" t="n">
-        <v>38.88</v>
-      </c>
+      <c r="O233" s="11" t="e"/>
       <c r="P233" s="10" t="n">
-        <v>114.48</v>
+        <v>145.44</v>
       </c>
       <c r="Q233" s="12" t="e"/>
     </row>
@@ -8969,33 +8995,37 @@
       </c>
       <c r="E234" s="8" t="e"/>
       <c r="F234" s="9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G234" s="9" t="e"/>
       <c r="H234" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I234" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J234" s="10" t="n">
-        <v>77.04</v>
+        <v>182.88</v>
       </c>
       <c r="K234" s="11" t="e"/>
       <c r="L234" s="11" t="e"/>
       <c r="M234" s="10" t="n">
-        <v>77.04</v>
-      </c>
-      <c r="N234" s="11" t="e"/>
+        <v>182.88</v>
+      </c>
+      <c r="N234" s="10" t="n">
+        <v>738.72</v>
+      </c>
       <c r="O234" s="11" t="e"/>
       <c r="P234" s="10" t="n">
-        <v>77.04</v>
-      </c>
-      <c r="Q234" s="12" t="e"/>
+        <v>921.6</v>
+      </c>
+      <c r="Q234" s="10" t="n">
+        <v>921.6</v>
+      </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="1">
       <c r="A235" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B235" s="7" t="e"/>
       <c r="C235" s="7" t="e"/>
@@ -9004,27 +9034,27 @@
       </c>
       <c r="E235" s="8" t="e"/>
       <c r="F235" s="9" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G235" s="9" t="e"/>
       <c r="H235" s="9" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I235" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J235" s="10" t="n">
-        <v>25.56</v>
+        <v>738.72</v>
       </c>
       <c r="K235" s="11" t="e"/>
       <c r="L235" s="11" t="e"/>
       <c r="M235" s="10" t="n">
-        <v>25.56</v>
+        <v>738.72</v>
       </c>
       <c r="N235" s="11" t="e"/>
       <c r="O235" s="11" t="e"/>
       <c r="P235" s="10" t="n">
-        <v>25.56</v>
+        <v>738.72</v>
       </c>
       <c r="Q235" s="12" t="e"/>
     </row>
@@ -9039,29 +9069,33 @@
       </c>
       <c r="E236" s="8" t="e"/>
       <c r="F236" s="9" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G236" s="9" t="e"/>
       <c r="H236" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I236" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J236" s="10" t="n">
-        <v>866.88</v>
+        <v>45.36</v>
       </c>
       <c r="K236" s="11" t="e"/>
       <c r="L236" s="11" t="e"/>
       <c r="M236" s="10" t="n">
-        <v>866.88</v>
-      </c>
-      <c r="N236" s="11" t="e"/>
+        <v>45.36</v>
+      </c>
+      <c r="N236" s="10" t="n">
+        <v>538.56</v>
+      </c>
       <c r="O236" s="11" t="e"/>
       <c r="P236" s="10" t="n">
-        <v>866.88</v>
-      </c>
-      <c r="Q236" s="12" t="e"/>
+        <v>583.92</v>
+      </c>
+      <c r="Q236" s="10" t="n">
+        <v>583.92</v>
+      </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="1">
       <c r="A237" s="7" t="n">
@@ -9074,33 +9108,33 @@
       </c>
       <c r="E237" s="8" t="e"/>
       <c r="F237" s="9" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G237" s="9" t="e"/>
       <c r="H237" s="9" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I237" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J237" s="10" t="n">
-        <v>469.44</v>
+        <v>457.2</v>
       </c>
       <c r="K237" s="11" t="e"/>
       <c r="L237" s="11" t="e"/>
       <c r="M237" s="10" t="n">
-        <v>469.44</v>
+        <v>457.2</v>
       </c>
       <c r="N237" s="11" t="e"/>
       <c r="O237" s="11" t="e"/>
       <c r="P237" s="10" t="n">
-        <v>469.44</v>
+        <v>457.2</v>
       </c>
       <c r="Q237" s="12" t="e"/>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="1">
       <c r="A238" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B238" s="7" t="e"/>
       <c r="C238" s="7" t="e"/>
@@ -9109,31 +9143,31 @@
       </c>
       <c r="E238" s="8" t="e"/>
       <c r="F238" s="9" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="G238" s="9" t="e"/>
       <c r="H238" s="9" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I238" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J238" s="10" t="n">
-        <v>78.51</v>
+        <v>153.36</v>
       </c>
       <c r="K238" s="11" t="e"/>
       <c r="L238" s="10" t="n">
-        <v>1.44</v>
+        <v>38.88</v>
       </c>
       <c r="M238" s="10" t="n">
-        <v>77.07</v>
+        <v>114.48</v>
       </c>
       <c r="N238" s="11" t="e"/>
       <c r="O238" s="10" t="n">
-        <v>1.44</v>
+        <v>38.88</v>
       </c>
       <c r="P238" s="10" t="n">
-        <v>77.07</v>
+        <v>114.48</v>
       </c>
       <c r="Q238" s="12" t="e"/>
     </row>
@@ -9148,37 +9182,33 @@
       </c>
       <c r="E239" s="8" t="e"/>
       <c r="F239" s="9" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G239" s="9" t="e"/>
       <c r="H239" s="9" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I239" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J239" s="10" t="n">
-        <v>29.52</v>
+        <v>77.04</v>
       </c>
       <c r="K239" s="11" t="e"/>
       <c r="L239" s="11" t="e"/>
       <c r="M239" s="10" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="N239" s="10" t="n">
-        <v>580.32</v>
-      </c>
+        <v>77.04</v>
+      </c>
+      <c r="N239" s="11" t="e"/>
       <c r="O239" s="11" t="e"/>
       <c r="P239" s="10" t="n">
-        <v>609.84</v>
-      </c>
-      <c r="Q239" s="10" t="n">
-        <v>609.84</v>
-      </c>
+        <v>77.04</v>
+      </c>
+      <c r="Q239" s="12" t="e"/>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="1">
       <c r="A240" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B240" s="7" t="e"/>
       <c r="C240" s="7" t="e"/>
@@ -9187,27 +9217,27 @@
       </c>
       <c r="E240" s="8" t="e"/>
       <c r="F240" s="9" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="G240" s="9" t="e"/>
       <c r="H240" s="9" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I240" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J240" s="10" t="n">
-        <v>357.84</v>
+        <v>25.56</v>
       </c>
       <c r="K240" s="11" t="e"/>
       <c r="L240" s="11" t="e"/>
       <c r="M240" s="10" t="n">
-        <v>357.84</v>
+        <v>25.56</v>
       </c>
       <c r="N240" s="11" t="e"/>
       <c r="O240" s="11" t="e"/>
       <c r="P240" s="10" t="n">
-        <v>357.84</v>
+        <v>25.56</v>
       </c>
       <c r="Q240" s="12" t="e"/>
     </row>
@@ -9222,27 +9252,27 @@
       </c>
       <c r="E241" s="8" t="e"/>
       <c r="F241" s="9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G241" s="9" t="e"/>
       <c r="H241" s="9" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="I241" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J241" s="10" t="n">
-        <v>180</v>
+        <v>866.88</v>
       </c>
       <c r="K241" s="11" t="e"/>
       <c r="L241" s="11" t="e"/>
       <c r="M241" s="10" t="n">
-        <v>180</v>
+        <v>866.88</v>
       </c>
       <c r="N241" s="11" t="e"/>
       <c r="O241" s="11" t="e"/>
       <c r="P241" s="10" t="n">
-        <v>180</v>
+        <v>866.88</v>
       </c>
       <c r="Q241" s="12" t="e"/>
     </row>
@@ -9257,27 +9287,27 @@
       </c>
       <c r="E242" s="8" t="e"/>
       <c r="F242" s="9" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="G242" s="9" t="e"/>
       <c r="H242" s="9" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="I242" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J242" s="10" t="n">
-        <v>3.6</v>
+        <v>469.44</v>
       </c>
       <c r="K242" s="11" t="e"/>
       <c r="L242" s="11" t="e"/>
       <c r="M242" s="10" t="n">
-        <v>3.6</v>
+        <v>469.44</v>
       </c>
       <c r="N242" s="11" t="e"/>
       <c r="O242" s="11" t="e"/>
       <c r="P242" s="10" t="n">
-        <v>3.6</v>
+        <v>469.44</v>
       </c>
       <c r="Q242" s="12" t="e"/>
     </row>
@@ -9292,33 +9322,33 @@
       </c>
       <c r="E243" s="8" t="e"/>
       <c r="F243" s="9" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G243" s="9" t="e"/>
       <c r="H243" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I243" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J243" s="10" t="n">
-        <v>5.76</v>
+        <v>78.51</v>
       </c>
       <c r="K243" s="11" t="e"/>
-      <c r="L243" s="11" t="e"/>
+      <c r="L243" s="10" t="n">
+        <v>1.44</v>
+      </c>
       <c r="M243" s="10" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="N243" s="19" t="n">
-        <v>1242.72</v>
-      </c>
-      <c r="O243" s="11" t="e"/>
-      <c r="P243" s="19" t="n">
-        <v>1248.48</v>
-      </c>
-      <c r="Q243" s="19" t="n">
-        <v>1248.48</v>
-      </c>
+        <v>77.07</v>
+      </c>
+      <c r="N243" s="11" t="e"/>
+      <c r="O243" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P243" s="10" t="n">
+        <v>77.07</v>
+      </c>
+      <c r="Q243" s="12" t="e"/>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="1">
       <c r="A244" s="7" t="n">
@@ -9331,29 +9361,33 @@
       </c>
       <c r="E244" s="8" t="e"/>
       <c r="F244" s="9" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G244" s="9" t="e"/>
       <c r="H244" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I244" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J244" s="10" t="n">
-        <v>31.68</v>
+        <v>29.52</v>
       </c>
       <c r="K244" s="11" t="e"/>
       <c r="L244" s="11" t="e"/>
       <c r="M244" s="10" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="N244" s="11" t="e"/>
+        <v>29.52</v>
+      </c>
+      <c r="N244" s="10" t="n">
+        <v>580.32</v>
+      </c>
       <c r="O244" s="11" t="e"/>
       <c r="P244" s="10" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="Q244" s="12" t="e"/>
+        <v>609.84</v>
+      </c>
+      <c r="Q244" s="10" t="n">
+        <v>609.84</v>
+      </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="1">
       <c r="A245" s="7" t="n">
@@ -9366,27 +9400,27 @@
       </c>
       <c r="E245" s="8" t="e"/>
       <c r="F245" s="9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G245" s="9" t="e"/>
       <c r="H245" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I245" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J245" s="10" t="n">
-        <v>177.84</v>
+        <v>357.84</v>
       </c>
       <c r="K245" s="11" t="e"/>
       <c r="L245" s="11" t="e"/>
       <c r="M245" s="10" t="n">
-        <v>177.84</v>
+        <v>357.84</v>
       </c>
       <c r="N245" s="11" t="e"/>
       <c r="O245" s="11" t="e"/>
       <c r="P245" s="10" t="n">
-        <v>177.84</v>
+        <v>357.84</v>
       </c>
       <c r="Q245" s="12" t="e"/>
     </row>
@@ -9401,27 +9435,27 @@
       </c>
       <c r="E246" s="8" t="e"/>
       <c r="F246" s="9" t="s">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="G246" s="9" t="e"/>
       <c r="H246" s="9" t="s">
-        <v>250</v>
+        <v>161</v>
       </c>
       <c r="I246" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J246" s="10" t="n">
-        <v>44.64</v>
+        <v>180</v>
       </c>
       <c r="K246" s="11" t="e"/>
       <c r="L246" s="11" t="e"/>
       <c r="M246" s="10" t="n">
-        <v>44.64</v>
+        <v>180</v>
       </c>
       <c r="N246" s="11" t="e"/>
       <c r="O246" s="11" t="e"/>
       <c r="P246" s="10" t="n">
-        <v>44.64</v>
+        <v>180</v>
       </c>
       <c r="Q246" s="12" t="e"/>
     </row>
@@ -9436,27 +9470,27 @@
       </c>
       <c r="E247" s="8" t="e"/>
       <c r="F247" s="9" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="G247" s="9" t="e"/>
       <c r="H247" s="9" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="I247" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J247" s="10" t="n">
-        <v>165.6</v>
+        <v>3.6</v>
       </c>
       <c r="K247" s="11" t="e"/>
       <c r="L247" s="11" t="e"/>
       <c r="M247" s="10" t="n">
-        <v>165.6</v>
+        <v>3.6</v>
       </c>
       <c r="N247" s="11" t="e"/>
       <c r="O247" s="11" t="e"/>
       <c r="P247" s="10" t="n">
-        <v>165.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q247" s="12" t="e"/>
     </row>
@@ -9471,33 +9505,33 @@
       </c>
       <c r="E248" s="8" t="e"/>
       <c r="F248" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="G248" s="9" t="e"/>
       <c r="H248" s="9" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I248" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J248" s="10" t="n">
-        <v>73.44</v>
-      </c>
-      <c r="K248" s="10" t="n">
-        <v>2.88</v>
-      </c>
+        <v>5.76</v>
+      </c>
+      <c r="K248" s="11" t="e"/>
       <c r="L248" s="11" t="e"/>
       <c r="M248" s="10" t="n">
-        <v>70.56</v>
-      </c>
-      <c r="N248" s="11" t="e"/>
-      <c r="O248" s="10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P248" s="10" t="n">
-        <v>70.56</v>
-      </c>
-      <c r="Q248" s="12" t="e"/>
+        <v>5.76</v>
+      </c>
+      <c r="N248" s="19" t="n">
+        <v>1242.72</v>
+      </c>
+      <c r="O248" s="11" t="e"/>
+      <c r="P248" s="19" t="n">
+        <v>1248.48</v>
+      </c>
+      <c r="Q248" s="19" t="n">
+        <v>1248.48</v>
+      </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="1">
       <c r="A249" s="7" t="n">
@@ -9510,217 +9544,241 @@
       </c>
       <c r="E249" s="8" t="e"/>
       <c r="F249" s="9" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="G249" s="9" t="e"/>
       <c r="H249" s="9" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="I249" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J249" s="10" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="J249" s="11" t="e"/>
       <c r="K249" s="11" t="e"/>
       <c r="L249" s="11" t="e"/>
-      <c r="M249" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N249" s="11" t="e"/>
+      <c r="M249" s="11" t="e"/>
+      <c r="N249" s="10" t="n">
+        <v>489.6</v>
+      </c>
       <c r="O249" s="11" t="e"/>
       <c r="P249" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Q249" s="12" t="e"/>
+        <v>489.6</v>
+      </c>
+      <c r="Q249" s="10" t="n">
+        <v>489.6</v>
+      </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A250" s="13" t="e"/>
-      <c r="B250" s="14" t="e"/>
-      <c r="C250" s="15" t="e"/>
-      <c r="D250" s="16" t="e"/>
-      <c r="E250" s="17" t="e"/>
+      <c r="A250" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B250" s="7" t="e"/>
+      <c r="C250" s="7" t="e"/>
+      <c r="D250" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E250" s="8" t="e"/>
       <c r="F250" s="9" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="G250" s="9" t="e"/>
       <c r="H250" s="9" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I250" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J250" s="10" t="n">
-        <v>9</v>
+        <v>31.68</v>
       </c>
       <c r="K250" s="11" t="e"/>
       <c r="L250" s="11" t="e"/>
       <c r="M250" s="10" t="n">
-        <v>9</v>
+        <v>31.68</v>
       </c>
       <c r="N250" s="11" t="e"/>
       <c r="O250" s="11" t="e"/>
       <c r="P250" s="10" t="n">
-        <v>9</v>
+        <v>31.68</v>
       </c>
       <c r="Q250" s="12" t="e"/>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A251" s="13" t="e"/>
-      <c r="B251" s="14" t="e"/>
-      <c r="C251" s="15" t="e"/>
-      <c r="D251" s="16" t="e"/>
-      <c r="E251" s="17" t="e"/>
+      <c r="A251" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B251" s="7" t="e"/>
+      <c r="C251" s="7" t="e"/>
+      <c r="D251" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E251" s="8" t="e"/>
       <c r="F251" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="G251" s="9" t="e"/>
       <c r="H251" s="9" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="I251" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J251" s="10" t="n">
-        <v>132</v>
+        <v>177.84</v>
       </c>
       <c r="K251" s="11" t="e"/>
       <c r="L251" s="11" t="e"/>
       <c r="M251" s="10" t="n">
-        <v>132</v>
+        <v>177.84</v>
       </c>
       <c r="N251" s="11" t="e"/>
       <c r="O251" s="11" t="e"/>
       <c r="P251" s="10" t="n">
-        <v>132</v>
+        <v>177.84</v>
       </c>
       <c r="Q251" s="12" t="e"/>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A252" s="13" t="e"/>
-      <c r="B252" s="14" t="e"/>
-      <c r="C252" s="15" t="e"/>
-      <c r="D252" s="16" t="e"/>
-      <c r="E252" s="17" t="e"/>
+      <c r="A252" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B252" s="7" t="e"/>
+      <c r="C252" s="7" t="e"/>
+      <c r="D252" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E252" s="8" t="e"/>
       <c r="F252" s="9" t="s">
-        <v>187</v>
+        <v>261</v>
       </c>
       <c r="G252" s="9" t="e"/>
       <c r="H252" s="9" t="s">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="I252" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J252" s="10" t="n">
-        <v>132</v>
+        <v>44.64</v>
       </c>
       <c r="K252" s="11" t="e"/>
       <c r="L252" s="11" t="e"/>
       <c r="M252" s="10" t="n">
-        <v>132</v>
+        <v>44.64</v>
       </c>
       <c r="N252" s="11" t="e"/>
       <c r="O252" s="11" t="e"/>
       <c r="P252" s="10" t="n">
-        <v>132</v>
+        <v>44.64</v>
       </c>
       <c r="Q252" s="12" t="e"/>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A253" s="13" t="e"/>
-      <c r="B253" s="14" t="e"/>
-      <c r="C253" s="15" t="e"/>
-      <c r="D253" s="16" t="e"/>
-      <c r="E253" s="17" t="e"/>
+      <c r="A253" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B253" s="7" t="e"/>
+      <c r="C253" s="7" t="e"/>
+      <c r="D253" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E253" s="8" t="e"/>
       <c r="F253" s="9" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="G253" s="9" t="e"/>
       <c r="H253" s="9" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="I253" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J253" s="10" t="n">
-        <v>79</v>
+        <v>165.6</v>
       </c>
       <c r="K253" s="11" t="e"/>
-      <c r="L253" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="L253" s="11" t="e"/>
       <c r="M253" s="10" t="n">
-        <v>62</v>
+        <v>165.6</v>
       </c>
       <c r="N253" s="11" t="e"/>
-      <c r="O253" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="O253" s="11" t="e"/>
       <c r="P253" s="10" t="n">
-        <v>62</v>
+        <v>165.6</v>
       </c>
       <c r="Q253" s="12" t="e"/>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A254" s="13" t="e"/>
-      <c r="B254" s="14" t="e"/>
-      <c r="C254" s="15" t="e"/>
-      <c r="D254" s="16" t="e"/>
-      <c r="E254" s="17" t="e"/>
+      <c r="A254" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B254" s="7" t="e"/>
+      <c r="C254" s="7" t="e"/>
+      <c r="D254" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E254" s="8" t="e"/>
       <c r="F254" s="9" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="G254" s="9" t="e"/>
       <c r="H254" s="9" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="I254" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J254" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="K254" s="11" t="e"/>
+        <v>73.44</v>
+      </c>
+      <c r="K254" s="10" t="n">
+        <v>2.88</v>
+      </c>
       <c r="L254" s="11" t="e"/>
       <c r="M254" s="10" t="n">
-        <v>42</v>
+        <v>70.56</v>
       </c>
       <c r="N254" s="11" t="e"/>
-      <c r="O254" s="11" t="e"/>
+      <c r="O254" s="10" t="n">
+        <v>2.88</v>
+      </c>
       <c r="P254" s="10" t="n">
-        <v>42</v>
+        <v>70.56</v>
       </c>
       <c r="Q254" s="12" t="e"/>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A255" s="13" t="e"/>
-      <c r="B255" s="14" t="e"/>
-      <c r="C255" s="15" t="e"/>
-      <c r="D255" s="16" t="e"/>
-      <c r="E255" s="17" t="e"/>
+      <c r="A255" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B255" s="7" t="e"/>
+      <c r="C255" s="7" t="e"/>
+      <c r="D255" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E255" s="8" t="e"/>
       <c r="F255" s="9" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="G255" s="9" t="e"/>
       <c r="H255" s="9" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="I255" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J255" s="10" t="n">
-        <v>101</v>
+        <v>16.2</v>
       </c>
       <c r="K255" s="11" t="e"/>
       <c r="L255" s="11" t="e"/>
       <c r="M255" s="10" t="n">
-        <v>101</v>
+        <v>16.2</v>
       </c>
       <c r="N255" s="11" t="e"/>
       <c r="O255" s="11" t="e"/>
       <c r="P255" s="10" t="n">
-        <v>101</v>
+        <v>16.2</v>
       </c>
       <c r="Q255" s="12" t="e"/>
     </row>
@@ -9731,27 +9789,27 @@
       <c r="D256" s="16" t="e"/>
       <c r="E256" s="17" t="e"/>
       <c r="F256" s="9" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G256" s="9" t="e"/>
       <c r="H256" s="9" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I256" s="9" t="s">
         <v>184</v>
       </c>
       <c r="J256" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K256" s="11" t="e"/>
       <c r="L256" s="11" t="e"/>
       <c r="M256" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N256" s="11" t="e"/>
       <c r="O256" s="11" t="e"/>
       <c r="P256" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q256" s="12" t="e"/>
     </row>
@@ -9762,31 +9820,27 @@
       <c r="D257" s="16" t="e"/>
       <c r="E257" s="17" t="e"/>
       <c r="F257" s="9" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G257" s="9" t="e"/>
       <c r="H257" s="9" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="I257" s="9" t="s">
         <v>184</v>
       </c>
       <c r="J257" s="10" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="K257" s="11" t="e"/>
-      <c r="L257" s="10" t="n">
-        <v>18</v>
-      </c>
+      <c r="L257" s="11" t="e"/>
       <c r="M257" s="10" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="N257" s="11" t="e"/>
-      <c r="O257" s="10" t="n">
-        <v>18</v>
-      </c>
+      <c r="O257" s="11" t="e"/>
       <c r="P257" s="10" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="Q257" s="12" t="e"/>
     </row>
@@ -9797,188 +9851,190 @@
       <c r="D258" s="16" t="e"/>
       <c r="E258" s="17" t="e"/>
       <c r="F258" s="9" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="G258" s="9" t="e"/>
       <c r="H258" s="9" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="I258" s="9" t="s">
         <v>184</v>
       </c>
       <c r="J258" s="10" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="K258" s="11" t="e"/>
       <c r="L258" s="11" t="e"/>
       <c r="M258" s="10" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="N258" s="11" t="e"/>
       <c r="O258" s="11" t="e"/>
       <c r="P258" s="10" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="Q258" s="12" t="e"/>
     </row>
-    <row r="259" ht="11" customHeight="true">
-      <c r="A259" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B259" s="5" t="e"/>
-      <c r="C259" s="5" t="e"/>
-      <c r="D259" s="5" t="e"/>
-      <c r="E259" s="5" t="e"/>
-      <c r="F259" s="5" t="e"/>
-      <c r="G259" s="5" t="e"/>
-      <c r="H259" s="5" t="e"/>
-      <c r="I259" s="5" t="e"/>
-      <c r="J259" s="6" t="e"/>
-      <c r="K259" s="6" t="e"/>
-      <c r="L259" s="6" t="e"/>
-      <c r="M259" s="6" t="e"/>
-      <c r="N259" s="6" t="e"/>
-      <c r="O259" s="6" t="e"/>
-      <c r="P259" s="6" t="e"/>
-      <c r="Q259" s="6" t="e"/>
+    <row r="259" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A259" s="13" t="e"/>
+      <c r="B259" s="14" t="e"/>
+      <c r="C259" s="15" t="e"/>
+      <c r="D259" s="16" t="e"/>
+      <c r="E259" s="17" t="e"/>
+      <c r="F259" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G259" s="9" t="e"/>
+      <c r="H259" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I259" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J259" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="K259" s="11" t="e"/>
+      <c r="L259" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="M259" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="N259" s="11" t="e"/>
+      <c r="O259" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="P259" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q259" s="12" t="e"/>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A260" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B260" s="7" t="e"/>
-      <c r="C260" s="7" t="e"/>
-      <c r="D260" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E260" s="8" t="e"/>
+      <c r="A260" s="13" t="e"/>
+      <c r="B260" s="14" t="e"/>
+      <c r="C260" s="15" t="e"/>
+      <c r="D260" s="16" t="e"/>
+      <c r="E260" s="17" t="e"/>
       <c r="F260" s="9" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="G260" s="9" t="e"/>
       <c r="H260" s="9" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="I260" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J260" s="10" t="n">
-        <v>2.88</v>
+        <v>42</v>
       </c>
       <c r="K260" s="11" t="e"/>
       <c r="L260" s="11" t="e"/>
       <c r="M260" s="10" t="n">
-        <v>2.88</v>
+        <v>42</v>
       </c>
       <c r="N260" s="11" t="e"/>
       <c r="O260" s="11" t="e"/>
       <c r="P260" s="10" t="n">
-        <v>2.88</v>
+        <v>42</v>
       </c>
       <c r="Q260" s="12" t="e"/>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A261" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B261" s="7" t="e"/>
-      <c r="C261" s="7" t="e"/>
-      <c r="D261" s="8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E261" s="8" t="e"/>
+      <c r="A261" s="13" t="e"/>
+      <c r="B261" s="14" t="e"/>
+      <c r="C261" s="15" t="e"/>
+      <c r="D261" s="16" t="e"/>
+      <c r="E261" s="17" t="e"/>
       <c r="F261" s="9" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G261" s="9" t="e"/>
       <c r="H261" s="9" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="I261" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J261" s="10" t="n">
-        <v>26.64</v>
+        <v>101</v>
       </c>
       <c r="K261" s="11" t="e"/>
       <c r="L261" s="11" t="e"/>
       <c r="M261" s="10" t="n">
-        <v>26.64</v>
+        <v>101</v>
       </c>
       <c r="N261" s="11" t="e"/>
       <c r="O261" s="11" t="e"/>
       <c r="P261" s="10" t="n">
-        <v>26.64</v>
+        <v>101</v>
       </c>
       <c r="Q261" s="12" t="e"/>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A262" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B262" s="7" t="e"/>
-      <c r="C262" s="7" t="e"/>
-      <c r="D262" s="8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E262" s="8" t="e"/>
+      <c r="A262" s="13" t="e"/>
+      <c r="B262" s="14" t="e"/>
+      <c r="C262" s="15" t="e"/>
+      <c r="D262" s="16" t="e"/>
+      <c r="E262" s="17" t="e"/>
       <c r="F262" s="9" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="G262" s="9" t="e"/>
       <c r="H262" s="9" t="s">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="I262" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J262" s="10" t="n">
-        <v>11.52</v>
+        <v>3</v>
       </c>
       <c r="K262" s="11" t="e"/>
       <c r="L262" s="11" t="e"/>
       <c r="M262" s="10" t="n">
-        <v>11.52</v>
+        <v>3</v>
       </c>
       <c r="N262" s="11" t="e"/>
       <c r="O262" s="11" t="e"/>
       <c r="P262" s="10" t="n">
-        <v>11.52</v>
+        <v>3</v>
       </c>
       <c r="Q262" s="12" t="e"/>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A263" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B263" s="7" t="e"/>
-      <c r="C263" s="7" t="e"/>
-      <c r="D263" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E263" s="8" t="e"/>
+      <c r="A263" s="13" t="e"/>
+      <c r="B263" s="14" t="e"/>
+      <c r="C263" s="15" t="e"/>
+      <c r="D263" s="16" t="e"/>
+      <c r="E263" s="17" t="e"/>
       <c r="F263" s="9" t="s">
-        <v>29</v>
+        <v>199</v>
       </c>
       <c r="G263" s="9" t="e"/>
       <c r="H263" s="9" t="s">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I263" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J263" s="10" t="n">
-        <v>5.76</v>
+        <v>78</v>
       </c>
       <c r="K263" s="11" t="e"/>
-      <c r="L263" s="11" t="e"/>
+      <c r="L263" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="M263" s="10" t="n">
-        <v>5.76</v>
+        <v>60</v>
       </c>
       <c r="N263" s="11" t="e"/>
-      <c r="O263" s="11" t="e"/>
+      <c r="O263" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="P263" s="10" t="n">
-        <v>5.76</v>
+        <v>60</v>
       </c>
       <c r="Q263" s="12" t="e"/>
     </row>
@@ -9989,64 +10045,50 @@
       <c r="D264" s="16" t="e"/>
       <c r="E264" s="17" t="e"/>
       <c r="F264" s="9" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="G264" s="9" t="e"/>
       <c r="H264" s="9" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="I264" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J264" s="10" t="n">
         <v>33</v>
-      </c>
-      <c r="J264" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="K264" s="11" t="e"/>
       <c r="L264" s="11" t="e"/>
       <c r="M264" s="10" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="N264" s="11" t="e"/>
       <c r="O264" s="11" t="e"/>
       <c r="P264" s="10" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Q264" s="12" t="e"/>
     </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A265" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B265" s="7" t="e"/>
-      <c r="C265" s="7" t="e"/>
-      <c r="D265" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E265" s="8" t="e"/>
-      <c r="F265" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G265" s="9" t="e"/>
-      <c r="H265" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I265" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J265" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K265" s="11" t="e"/>
-      <c r="L265" s="11" t="e"/>
-      <c r="M265" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N265" s="11" t="e"/>
-      <c r="O265" s="11" t="e"/>
-      <c r="P265" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q265" s="12" t="e"/>
+    <row r="265" ht="11" customHeight="true">
+      <c r="A265" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B265" s="5" t="e"/>
+      <c r="C265" s="5" t="e"/>
+      <c r="D265" s="5" t="e"/>
+      <c r="E265" s="5" t="e"/>
+      <c r="F265" s="5" t="e"/>
+      <c r="G265" s="5" t="e"/>
+      <c r="H265" s="5" t="e"/>
+      <c r="I265" s="5" t="e"/>
+      <c r="J265" s="6" t="e"/>
+      <c r="K265" s="6" t="e"/>
+      <c r="L265" s="6" t="e"/>
+      <c r="M265" s="6" t="e"/>
+      <c r="N265" s="6" t="e"/>
+      <c r="O265" s="6" t="e"/>
+      <c r="P265" s="6" t="e"/>
+      <c r="Q265" s="6" t="e"/>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="1">
       <c r="A266" s="7" t="n">
@@ -10059,103 +10101,103 @@
       </c>
       <c r="E266" s="8" t="e"/>
       <c r="F266" s="9" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G266" s="9" t="e"/>
       <c r="H266" s="9" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="I266" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J266" s="10" t="n">
-        <v>26.64</v>
+        <v>2.88</v>
       </c>
       <c r="K266" s="11" t="e"/>
       <c r="L266" s="11" t="e"/>
       <c r="M266" s="10" t="n">
-        <v>26.64</v>
+        <v>2.88</v>
       </c>
       <c r="N266" s="11" t="e"/>
       <c r="O266" s="11" t="e"/>
       <c r="P266" s="10" t="n">
-        <v>26.64</v>
+        <v>2.88</v>
       </c>
       <c r="Q266" s="12" t="e"/>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="1">
       <c r="A267" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B267" s="7" t="e"/>
       <c r="C267" s="7" t="e"/>
       <c r="D267" s="8" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="E267" s="8" t="e"/>
       <c r="F267" s="9" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="G267" s="9" t="e"/>
       <c r="H267" s="9" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="I267" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J267" s="10" t="n">
-        <v>0.72</v>
+        <v>26.64</v>
       </c>
       <c r="K267" s="11" t="e"/>
       <c r="L267" s="11" t="e"/>
       <c r="M267" s="10" t="n">
-        <v>0.72</v>
+        <v>26.64</v>
       </c>
       <c r="N267" s="11" t="e"/>
       <c r="O267" s="11" t="e"/>
       <c r="P267" s="10" t="n">
-        <v>0.72</v>
+        <v>26.64</v>
       </c>
       <c r="Q267" s="12" t="e"/>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="1">
       <c r="A268" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B268" s="7" t="e"/>
       <c r="C268" s="7" t="e"/>
       <c r="D268" s="8" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="E268" s="8" t="e"/>
       <c r="F268" s="9" t="s">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="G268" s="9" t="e"/>
       <c r="H268" s="9" t="s">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="I268" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J268" s="10" t="n">
-        <v>1.44</v>
+        <v>11.52</v>
       </c>
       <c r="K268" s="11" t="e"/>
       <c r="L268" s="11" t="e"/>
       <c r="M268" s="10" t="n">
-        <v>1.44</v>
+        <v>11.52</v>
       </c>
       <c r="N268" s="11" t="e"/>
       <c r="O268" s="11" t="e"/>
       <c r="P268" s="10" t="n">
-        <v>1.44</v>
+        <v>11.52</v>
       </c>
       <c r="Q268" s="12" t="e"/>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="1">
       <c r="A269" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B269" s="7" t="e"/>
       <c r="C269" s="7" t="e"/>
@@ -10164,62 +10206,58 @@
       </c>
       <c r="E269" s="8" t="e"/>
       <c r="F269" s="9" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="G269" s="9" t="e"/>
       <c r="H269" s="9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I269" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J269" s="10" t="n">
-        <v>2.16</v>
+        <v>5.76</v>
       </c>
       <c r="K269" s="11" t="e"/>
       <c r="L269" s="11" t="e"/>
       <c r="M269" s="10" t="n">
-        <v>2.16</v>
+        <v>5.76</v>
       </c>
       <c r="N269" s="11" t="e"/>
       <c r="O269" s="11" t="e"/>
       <c r="P269" s="10" t="n">
-        <v>2.16</v>
+        <v>5.76</v>
       </c>
       <c r="Q269" s="12" t="e"/>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A270" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B270" s="7" t="e"/>
-      <c r="C270" s="7" t="e"/>
-      <c r="D270" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E270" s="8" t="e"/>
+      <c r="A270" s="13" t="e"/>
+      <c r="B270" s="14" t="e"/>
+      <c r="C270" s="15" t="e"/>
+      <c r="D270" s="16" t="e"/>
+      <c r="E270" s="17" t="e"/>
       <c r="F270" s="9" t="s">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="G270" s="9" t="e"/>
       <c r="H270" s="9" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="I270" s="9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J270" s="10" t="n">
-        <v>18.36</v>
+        <v>1</v>
       </c>
       <c r="K270" s="11" t="e"/>
       <c r="L270" s="11" t="e"/>
       <c r="M270" s="10" t="n">
-        <v>18.36</v>
+        <v>1</v>
       </c>
       <c r="N270" s="11" t="e"/>
       <c r="O270" s="11" t="e"/>
       <c r="P270" s="10" t="n">
-        <v>18.36</v>
+        <v>1</v>
       </c>
       <c r="Q270" s="12" t="e"/>
     </row>
@@ -10234,27 +10272,27 @@
       </c>
       <c r="E271" s="8" t="e"/>
       <c r="F271" s="9" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G271" s="9" t="e"/>
       <c r="H271" s="9" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I271" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J271" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K271" s="11" t="e"/>
       <c r="L271" s="11" t="e"/>
       <c r="M271" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N271" s="11" t="e"/>
       <c r="O271" s="11" t="e"/>
       <c r="P271" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q271" s="12" t="e"/>
     </row>
@@ -10269,33 +10307,33 @@
       </c>
       <c r="E272" s="8" t="e"/>
       <c r="F272" s="9" t="s">
-        <v>205</v>
+        <v>68</v>
       </c>
       <c r="G272" s="9" t="e"/>
       <c r="H272" s="9" t="s">
-        <v>206</v>
+        <v>69</v>
       </c>
       <c r="I272" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J272" s="10" t="n">
-        <v>5.04</v>
+        <v>26.64</v>
       </c>
       <c r="K272" s="11" t="e"/>
       <c r="L272" s="11" t="e"/>
       <c r="M272" s="10" t="n">
-        <v>5.04</v>
+        <v>26.64</v>
       </c>
       <c r="N272" s="11" t="e"/>
       <c r="O272" s="11" t="e"/>
       <c r="P272" s="10" t="n">
-        <v>5.04</v>
+        <v>26.64</v>
       </c>
       <c r="Q272" s="12" t="e"/>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="1">
       <c r="A273" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B273" s="7" t="e"/>
       <c r="C273" s="7" t="e"/>
@@ -10304,27 +10342,27 @@
       </c>
       <c r="E273" s="8" t="e"/>
       <c r="F273" s="9" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G273" s="9" t="e"/>
       <c r="H273" s="9" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I273" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J273" s="10" t="n">
-        <v>46.08</v>
+        <v>0.72</v>
       </c>
       <c r="K273" s="11" t="e"/>
       <c r="L273" s="11" t="e"/>
       <c r="M273" s="10" t="n">
-        <v>46.08</v>
+        <v>0.72</v>
       </c>
       <c r="N273" s="11" t="e"/>
       <c r="O273" s="11" t="e"/>
       <c r="P273" s="10" t="n">
-        <v>46.08</v>
+        <v>0.72</v>
       </c>
       <c r="Q273" s="12" t="e"/>
     </row>
@@ -10339,27 +10377,27 @@
       </c>
       <c r="E274" s="8" t="e"/>
       <c r="F274" s="9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G274" s="9" t="e"/>
       <c r="H274" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I274" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J274" s="10" t="n">
-        <v>23.04</v>
+        <v>1.44</v>
       </c>
       <c r="K274" s="11" t="e"/>
       <c r="L274" s="11" t="e"/>
       <c r="M274" s="10" t="n">
-        <v>23.04</v>
+        <v>1.44</v>
       </c>
       <c r="N274" s="11" t="e"/>
       <c r="O274" s="11" t="e"/>
       <c r="P274" s="10" t="n">
-        <v>23.04</v>
+        <v>1.44</v>
       </c>
       <c r="Q274" s="12" t="e"/>
     </row>
@@ -10374,11 +10412,11 @@
       </c>
       <c r="E275" s="8" t="e"/>
       <c r="F275" s="9" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G275" s="9" t="e"/>
       <c r="H275" s="9" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I275" s="9" t="s">
         <v>22</v>
@@ -10400,7 +10438,7 @@
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="1">
       <c r="A276" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B276" s="7" t="e"/>
       <c r="C276" s="7" t="e"/>
@@ -10409,27 +10447,27 @@
       </c>
       <c r="E276" s="8" t="e"/>
       <c r="F276" s="9" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G276" s="9" t="e"/>
       <c r="H276" s="9" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="I276" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J276" s="10" t="n">
-        <v>13.68</v>
+        <v>18.36</v>
       </c>
       <c r="K276" s="11" t="e"/>
       <c r="L276" s="11" t="e"/>
       <c r="M276" s="10" t="n">
-        <v>13.68</v>
+        <v>18.36</v>
       </c>
       <c r="N276" s="11" t="e"/>
       <c r="O276" s="11" t="e"/>
       <c r="P276" s="10" t="n">
-        <v>13.68</v>
+        <v>18.36</v>
       </c>
       <c r="Q276" s="12" t="e"/>
     </row>
@@ -10444,33 +10482,33 @@
       </c>
       <c r="E277" s="8" t="e"/>
       <c r="F277" s="9" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G277" s="9" t="e"/>
       <c r="H277" s="9" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="I277" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J277" s="10" t="n">
-        <v>54</v>
+        <v>0.72</v>
       </c>
       <c r="K277" s="11" t="e"/>
       <c r="L277" s="11" t="e"/>
       <c r="M277" s="10" t="n">
-        <v>54</v>
+        <v>0.72</v>
       </c>
       <c r="N277" s="11" t="e"/>
       <c r="O277" s="11" t="e"/>
       <c r="P277" s="10" t="n">
-        <v>54</v>
+        <v>0.72</v>
       </c>
       <c r="Q277" s="12" t="e"/>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="1">
       <c r="A278" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B278" s="7" t="e"/>
       <c r="C278" s="7" t="e"/>
@@ -10479,27 +10517,27 @@
       </c>
       <c r="E278" s="8" t="e"/>
       <c r="F278" s="9" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
       <c r="G278" s="9" t="e"/>
       <c r="H278" s="9" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="I278" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J278" s="10" t="n">
-        <v>32.76</v>
+        <v>5.04</v>
       </c>
       <c r="K278" s="11" t="e"/>
       <c r="L278" s="11" t="e"/>
       <c r="M278" s="10" t="n">
-        <v>32.76</v>
+        <v>5.04</v>
       </c>
       <c r="N278" s="11" t="e"/>
       <c r="O278" s="11" t="e"/>
       <c r="P278" s="10" t="n">
-        <v>32.76</v>
+        <v>5.04</v>
       </c>
       <c r="Q278" s="12" t="e"/>
     </row>
@@ -10514,27 +10552,27 @@
       </c>
       <c r="E279" s="8" t="e"/>
       <c r="F279" s="9" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G279" s="9" t="e"/>
       <c r="H279" s="9" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="I279" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J279" s="10" t="n">
-        <v>1.08</v>
+        <v>46.08</v>
       </c>
       <c r="K279" s="11" t="e"/>
       <c r="L279" s="11" t="e"/>
       <c r="M279" s="10" t="n">
-        <v>1.08</v>
+        <v>46.08</v>
       </c>
       <c r="N279" s="11" t="e"/>
       <c r="O279" s="11" t="e"/>
       <c r="P279" s="10" t="n">
-        <v>1.08</v>
+        <v>46.08</v>
       </c>
       <c r="Q279" s="12" t="e"/>
     </row>
@@ -10549,27 +10587,27 @@
       </c>
       <c r="E280" s="8" t="e"/>
       <c r="F280" s="9" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="G280" s="9" t="e"/>
       <c r="H280" s="9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="I280" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J280" s="10" t="n">
-        <v>0.72</v>
+        <v>23.04</v>
       </c>
       <c r="K280" s="11" t="e"/>
       <c r="L280" s="11" t="e"/>
       <c r="M280" s="10" t="n">
-        <v>0.72</v>
+        <v>23.04</v>
       </c>
       <c r="N280" s="11" t="e"/>
       <c r="O280" s="11" t="e"/>
       <c r="P280" s="10" t="n">
-        <v>0.72</v>
+        <v>23.04</v>
       </c>
       <c r="Q280" s="12" t="e"/>
     </row>
@@ -10584,11 +10622,11 @@
       </c>
       <c r="E281" s="8" t="e"/>
       <c r="F281" s="9" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G281" s="9" t="e"/>
       <c r="H281" s="9" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I281" s="9" t="s">
         <v>22</v>
@@ -10610,7 +10648,7 @@
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="1">
       <c r="A282" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B282" s="7" t="e"/>
       <c r="C282" s="7" t="e"/>
@@ -10619,33 +10657,33 @@
       </c>
       <c r="E282" s="8" t="e"/>
       <c r="F282" s="9" t="s">
-        <v>247</v>
+        <v>96</v>
       </c>
       <c r="G282" s="9" t="e"/>
       <c r="H282" s="9" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="I282" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J282" s="10" t="n">
-        <v>0.36</v>
+        <v>13.68</v>
       </c>
       <c r="K282" s="11" t="e"/>
       <c r="L282" s="11" t="e"/>
       <c r="M282" s="10" t="n">
-        <v>0.36</v>
+        <v>13.68</v>
       </c>
       <c r="N282" s="11" t="e"/>
       <c r="O282" s="11" t="e"/>
       <c r="P282" s="10" t="n">
-        <v>0.36</v>
+        <v>13.68</v>
       </c>
       <c r="Q282" s="12" t="e"/>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="1">
       <c r="A283" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B283" s="7" t="e"/>
       <c r="C283" s="7" t="e"/>
@@ -10654,33 +10692,33 @@
       </c>
       <c r="E283" s="8" t="e"/>
       <c r="F283" s="9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="G283" s="9" t="e"/>
       <c r="H283" s="9" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="I283" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J283" s="10" t="n">
-        <v>92.52</v>
+        <v>54</v>
       </c>
       <c r="K283" s="11" t="e"/>
       <c r="L283" s="11" t="e"/>
       <c r="M283" s="10" t="n">
-        <v>92.52</v>
+        <v>54</v>
       </c>
       <c r="N283" s="11" t="e"/>
       <c r="O283" s="11" t="e"/>
       <c r="P283" s="10" t="n">
-        <v>92.52</v>
+        <v>54</v>
       </c>
       <c r="Q283" s="12" t="e"/>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="1">
       <c r="A284" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B284" s="7" t="e"/>
       <c r="C284" s="7" t="e"/>
@@ -10689,27 +10727,27 @@
       </c>
       <c r="E284" s="8" t="e"/>
       <c r="F284" s="9" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G284" s="9" t="e"/>
       <c r="H284" s="9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="I284" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J284" s="10" t="n">
-        <v>2.16</v>
+        <v>32.76</v>
       </c>
       <c r="K284" s="11" t="e"/>
       <c r="L284" s="11" t="e"/>
       <c r="M284" s="10" t="n">
-        <v>2.16</v>
+        <v>32.76</v>
       </c>
       <c r="N284" s="11" t="e"/>
       <c r="O284" s="11" t="e"/>
       <c r="P284" s="10" t="n">
-        <v>2.16</v>
+        <v>32.76</v>
       </c>
       <c r="Q284" s="12" t="e"/>
     </row>
@@ -10724,27 +10762,27 @@
       </c>
       <c r="E285" s="8" t="e"/>
       <c r="F285" s="9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G285" s="9" t="e"/>
       <c r="H285" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I285" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J285" s="10" t="n">
-        <v>16.2</v>
+        <v>1.08</v>
       </c>
       <c r="K285" s="11" t="e"/>
       <c r="L285" s="11" t="e"/>
       <c r="M285" s="10" t="n">
-        <v>16.2</v>
+        <v>1.08</v>
       </c>
       <c r="N285" s="11" t="e"/>
       <c r="O285" s="11" t="e"/>
       <c r="P285" s="10" t="n">
-        <v>16.2</v>
+        <v>1.08</v>
       </c>
       <c r="Q285" s="12" t="e"/>
     </row>
@@ -10759,27 +10797,27 @@
       </c>
       <c r="E286" s="8" t="e"/>
       <c r="F286" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G286" s="9" t="e"/>
       <c r="H286" s="9" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="I286" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J286" s="10" t="n">
-        <v>45.36</v>
+        <v>0.72</v>
       </c>
       <c r="K286" s="11" t="e"/>
       <c r="L286" s="11" t="e"/>
       <c r="M286" s="10" t="n">
-        <v>45.36</v>
+        <v>0.72</v>
       </c>
       <c r="N286" s="11" t="e"/>
       <c r="O286" s="11" t="e"/>
       <c r="P286" s="10" t="n">
-        <v>45.36</v>
+        <v>0.72</v>
       </c>
       <c r="Q286" s="12" t="e"/>
     </row>
@@ -10794,33 +10832,33 @@
       </c>
       <c r="E287" s="8" t="e"/>
       <c r="F287" s="9" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="G287" s="9" t="e"/>
       <c r="H287" s="9" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I287" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J287" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="K287" s="11" t="e"/>
       <c r="L287" s="11" t="e"/>
       <c r="M287" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="N287" s="11" t="e"/>
       <c r="O287" s="11" t="e"/>
       <c r="P287" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="Q287" s="12" t="e"/>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="1">
       <c r="A288" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B288" s="7" t="e"/>
       <c r="C288" s="7" t="e"/>
@@ -10829,33 +10867,33 @@
       </c>
       <c r="E288" s="8" t="e"/>
       <c r="F288" s="9" t="s">
-        <v>132</v>
+        <v>257</v>
       </c>
       <c r="G288" s="9" t="e"/>
       <c r="H288" s="9" t="s">
-        <v>133</v>
+        <v>258</v>
       </c>
       <c r="I288" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J288" s="10" t="n">
-        <v>43.2</v>
+        <v>0.36</v>
       </c>
       <c r="K288" s="11" t="e"/>
       <c r="L288" s="11" t="e"/>
       <c r="M288" s="10" t="n">
-        <v>43.2</v>
+        <v>0.36</v>
       </c>
       <c r="N288" s="11" t="e"/>
       <c r="O288" s="11" t="e"/>
       <c r="P288" s="10" t="n">
-        <v>43.2</v>
+        <v>0.36</v>
       </c>
       <c r="Q288" s="12" t="e"/>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="1">
       <c r="A289" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B289" s="7" t="e"/>
       <c r="C289" s="7" t="e"/>
@@ -10864,27 +10902,27 @@
       </c>
       <c r="E289" s="8" t="e"/>
       <c r="F289" s="9" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G289" s="9" t="e"/>
       <c r="H289" s="9" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="I289" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J289" s="10" t="n">
-        <v>44.64</v>
+        <v>92.52</v>
       </c>
       <c r="K289" s="11" t="e"/>
       <c r="L289" s="11" t="e"/>
       <c r="M289" s="10" t="n">
-        <v>44.64</v>
+        <v>92.52</v>
       </c>
       <c r="N289" s="11" t="e"/>
       <c r="O289" s="11" t="e"/>
       <c r="P289" s="10" t="n">
-        <v>44.64</v>
+        <v>92.52</v>
       </c>
       <c r="Q289" s="12" t="e"/>
     </row>
@@ -10899,33 +10937,33 @@
       </c>
       <c r="E290" s="8" t="e"/>
       <c r="F290" s="9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G290" s="9" t="e"/>
       <c r="H290" s="9" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="I290" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J290" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="K290" s="11" t="e"/>
       <c r="L290" s="11" t="e"/>
       <c r="M290" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="N290" s="11" t="e"/>
       <c r="O290" s="11" t="e"/>
       <c r="P290" s="10" t="n">
-        <v>44.64</v>
+        <v>2.16</v>
       </c>
       <c r="Q290" s="12" t="e"/>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="1">
       <c r="A291" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B291" s="7" t="e"/>
       <c r="C291" s="7" t="e"/>
@@ -10934,27 +10972,27 @@
       </c>
       <c r="E291" s="8" t="e"/>
       <c r="F291" s="9" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="G291" s="9" t="e"/>
       <c r="H291" s="9" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I291" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J291" s="10" t="n">
-        <v>1.44</v>
+        <v>16.2</v>
       </c>
       <c r="K291" s="11" t="e"/>
       <c r="L291" s="11" t="e"/>
       <c r="M291" s="10" t="n">
-        <v>1.44</v>
+        <v>16.2</v>
       </c>
       <c r="N291" s="11" t="e"/>
       <c r="O291" s="11" t="e"/>
       <c r="P291" s="10" t="n">
-        <v>1.44</v>
+        <v>16.2</v>
       </c>
       <c r="Q291" s="12" t="e"/>
     </row>
@@ -10969,27 +11007,27 @@
       </c>
       <c r="E292" s="8" t="e"/>
       <c r="F292" s="9" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="G292" s="9" t="e"/>
       <c r="H292" s="9" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I292" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J292" s="10" t="n">
-        <v>5.04</v>
+        <v>45.36</v>
       </c>
       <c r="K292" s="11" t="e"/>
       <c r="L292" s="11" t="e"/>
       <c r="M292" s="10" t="n">
-        <v>5.04</v>
+        <v>45.36</v>
       </c>
       <c r="N292" s="11" t="e"/>
       <c r="O292" s="11" t="e"/>
       <c r="P292" s="10" t="n">
-        <v>5.04</v>
+        <v>45.36</v>
       </c>
       <c r="Q292" s="12" t="e"/>
     </row>
@@ -11004,33 +11042,33 @@
       </c>
       <c r="E293" s="8" t="e"/>
       <c r="F293" s="9" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="G293" s="9" t="e"/>
       <c r="H293" s="9" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="I293" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J293" s="10" t="n">
-        <v>11.52</v>
+        <v>44.64</v>
       </c>
       <c r="K293" s="11" t="e"/>
       <c r="L293" s="11" t="e"/>
       <c r="M293" s="10" t="n">
-        <v>11.52</v>
+        <v>44.64</v>
       </c>
       <c r="N293" s="11" t="e"/>
       <c r="O293" s="11" t="e"/>
       <c r="P293" s="10" t="n">
-        <v>11.52</v>
+        <v>44.64</v>
       </c>
       <c r="Q293" s="12" t="e"/>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="1">
       <c r="A294" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B294" s="7" t="e"/>
       <c r="C294" s="7" t="e"/>
@@ -11039,33 +11077,33 @@
       </c>
       <c r="E294" s="8" t="e"/>
       <c r="F294" s="9" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G294" s="9" t="e"/>
       <c r="H294" s="9" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I294" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J294" s="10" t="n">
-        <v>58.68</v>
+        <v>43.2</v>
       </c>
       <c r="K294" s="11" t="e"/>
       <c r="L294" s="11" t="e"/>
       <c r="M294" s="10" t="n">
-        <v>58.68</v>
+        <v>43.2</v>
       </c>
       <c r="N294" s="11" t="e"/>
       <c r="O294" s="11" t="e"/>
       <c r="P294" s="10" t="n">
-        <v>58.68</v>
+        <v>43.2</v>
       </c>
       <c r="Q294" s="12" t="e"/>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="1">
       <c r="A295" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B295" s="7" t="e"/>
       <c r="C295" s="7" t="e"/>
@@ -11074,27 +11112,27 @@
       </c>
       <c r="E295" s="8" t="e"/>
       <c r="F295" s="9" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="G295" s="9" t="e"/>
       <c r="H295" s="9" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="I295" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J295" s="10" t="n">
-        <v>91.8</v>
+        <v>44.64</v>
       </c>
       <c r="K295" s="11" t="e"/>
       <c r="L295" s="11" t="e"/>
       <c r="M295" s="10" t="n">
-        <v>91.8</v>
+        <v>44.64</v>
       </c>
       <c r="N295" s="11" t="e"/>
       <c r="O295" s="11" t="e"/>
       <c r="P295" s="10" t="n">
-        <v>91.8</v>
+        <v>44.64</v>
       </c>
       <c r="Q295" s="12" t="e"/>
     </row>
@@ -11109,27 +11147,27 @@
       </c>
       <c r="E296" s="8" t="e"/>
       <c r="F296" s="9" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G296" s="9" t="e"/>
       <c r="H296" s="9" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I296" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J296" s="10" t="n">
-        <v>1.44</v>
+        <v>44.64</v>
       </c>
       <c r="K296" s="11" t="e"/>
       <c r="L296" s="11" t="e"/>
       <c r="M296" s="10" t="n">
-        <v>1.44</v>
+        <v>44.64</v>
       </c>
       <c r="N296" s="11" t="e"/>
       <c r="O296" s="11" t="e"/>
       <c r="P296" s="10" t="n">
-        <v>1.44</v>
+        <v>44.64</v>
       </c>
       <c r="Q296" s="12" t="e"/>
     </row>
@@ -11144,27 +11182,27 @@
       </c>
       <c r="E297" s="8" t="e"/>
       <c r="F297" s="9" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G297" s="9" t="e"/>
       <c r="H297" s="9" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I297" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J297" s="10" t="n">
-        <v>28.8</v>
+        <v>1.44</v>
       </c>
       <c r="K297" s="11" t="e"/>
       <c r="L297" s="11" t="e"/>
       <c r="M297" s="10" t="n">
-        <v>28.8</v>
+        <v>1.44</v>
       </c>
       <c r="N297" s="11" t="e"/>
       <c r="O297" s="11" t="e"/>
       <c r="P297" s="10" t="n">
-        <v>28.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q297" s="12" t="e"/>
     </row>
@@ -11179,11 +11217,11 @@
       </c>
       <c r="E298" s="8" t="e"/>
       <c r="F298" s="9" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="G298" s="9" t="e"/>
       <c r="H298" s="9" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="I298" s="9" t="s">
         <v>22</v>
@@ -11214,33 +11252,33 @@
       </c>
       <c r="E299" s="8" t="e"/>
       <c r="F299" s="9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G299" s="9" t="e"/>
       <c r="H299" s="9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="I299" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J299" s="10" t="n">
-        <v>0.72</v>
+        <v>11.52</v>
       </c>
       <c r="K299" s="11" t="e"/>
       <c r="L299" s="11" t="e"/>
       <c r="M299" s="10" t="n">
-        <v>0.72</v>
+        <v>11.52</v>
       </c>
       <c r="N299" s="11" t="e"/>
       <c r="O299" s="11" t="e"/>
       <c r="P299" s="10" t="n">
-        <v>0.72</v>
+        <v>11.52</v>
       </c>
       <c r="Q299" s="12" t="e"/>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="1">
       <c r="A300" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B300" s="7" t="e"/>
       <c r="C300" s="7" t="e"/>
@@ -11249,33 +11287,33 @@
       </c>
       <c r="E300" s="8" t="e"/>
       <c r="F300" s="9" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="G300" s="9" t="e"/>
       <c r="H300" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I300" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J300" s="10" t="n">
-        <v>16.56</v>
+        <v>58.68</v>
       </c>
       <c r="K300" s="11" t="e"/>
       <c r="L300" s="11" t="e"/>
       <c r="M300" s="10" t="n">
-        <v>16.56</v>
+        <v>58.68</v>
       </c>
       <c r="N300" s="11" t="e"/>
       <c r="O300" s="11" t="e"/>
       <c r="P300" s="10" t="n">
-        <v>16.56</v>
+        <v>58.68</v>
       </c>
       <c r="Q300" s="12" t="e"/>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="1">
       <c r="A301" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B301" s="7" t="e"/>
       <c r="C301" s="7" t="e"/>
@@ -11284,27 +11322,27 @@
       </c>
       <c r="E301" s="8" t="e"/>
       <c r="F301" s="9" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="G301" s="9" t="e"/>
       <c r="H301" s="9" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I301" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J301" s="10" t="n">
-        <v>31.68</v>
+        <v>91.8</v>
       </c>
       <c r="K301" s="11" t="e"/>
       <c r="L301" s="11" t="e"/>
       <c r="M301" s="10" t="n">
-        <v>31.68</v>
+        <v>91.8</v>
       </c>
       <c r="N301" s="11" t="e"/>
       <c r="O301" s="11" t="e"/>
       <c r="P301" s="10" t="n">
-        <v>31.68</v>
+        <v>91.8</v>
       </c>
       <c r="Q301" s="12" t="e"/>
     </row>
@@ -11319,11 +11357,11 @@
       </c>
       <c r="E302" s="8" t="e"/>
       <c r="F302" s="9" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G302" s="9" t="e"/>
       <c r="H302" s="9" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I302" s="9" t="s">
         <v>22</v>
@@ -11354,27 +11392,27 @@
       </c>
       <c r="E303" s="8" t="e"/>
       <c r="F303" s="9" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G303" s="9" t="e"/>
       <c r="H303" s="9" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I303" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J303" s="10" t="n">
-        <v>7.92</v>
+        <v>28.8</v>
       </c>
       <c r="K303" s="11" t="e"/>
       <c r="L303" s="11" t="e"/>
       <c r="M303" s="10" t="n">
-        <v>7.92</v>
+        <v>28.8</v>
       </c>
       <c r="N303" s="11" t="e"/>
       <c r="O303" s="11" t="e"/>
       <c r="P303" s="10" t="n">
-        <v>7.92</v>
+        <v>28.8</v>
       </c>
       <c r="Q303" s="12" t="e"/>
     </row>
@@ -11389,27 +11427,27 @@
       </c>
       <c r="E304" s="8" t="e"/>
       <c r="F304" s="9" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="G304" s="9" t="e"/>
       <c r="H304" s="9" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I304" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J304" s="10" t="n">
-        <v>45.36</v>
+        <v>5.04</v>
       </c>
       <c r="K304" s="11" t="e"/>
       <c r="L304" s="11" t="e"/>
       <c r="M304" s="10" t="n">
-        <v>45.36</v>
+        <v>5.04</v>
       </c>
       <c r="N304" s="11" t="e"/>
       <c r="O304" s="11" t="e"/>
       <c r="P304" s="10" t="n">
-        <v>45.36</v>
+        <v>5.04</v>
       </c>
       <c r="Q304" s="12" t="e"/>
     </row>
@@ -11424,27 +11462,27 @@
       </c>
       <c r="E305" s="8" t="e"/>
       <c r="F305" s="9" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G305" s="9" t="e"/>
       <c r="H305" s="9" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I305" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J305" s="10" t="n">
-        <v>41.04</v>
+        <v>0.72</v>
       </c>
       <c r="K305" s="11" t="e"/>
       <c r="L305" s="11" t="e"/>
       <c r="M305" s="10" t="n">
-        <v>41.04</v>
+        <v>0.72</v>
       </c>
       <c r="N305" s="11" t="e"/>
       <c r="O305" s="11" t="e"/>
       <c r="P305" s="10" t="n">
-        <v>41.04</v>
+        <v>0.72</v>
       </c>
       <c r="Q305" s="12" t="e"/>
     </row>
@@ -11459,27 +11497,27 @@
       </c>
       <c r="E306" s="8" t="e"/>
       <c r="F306" s="9" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G306" s="9" t="e"/>
       <c r="H306" s="9" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="I306" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J306" s="10" t="n">
-        <v>0.72</v>
+        <v>16.56</v>
       </c>
       <c r="K306" s="11" t="e"/>
       <c r="L306" s="11" t="e"/>
       <c r="M306" s="10" t="n">
-        <v>0.72</v>
+        <v>16.56</v>
       </c>
       <c r="N306" s="11" t="e"/>
       <c r="O306" s="11" t="e"/>
       <c r="P306" s="10" t="n">
-        <v>0.72</v>
+        <v>16.56</v>
       </c>
       <c r="Q306" s="12" t="e"/>
     </row>
@@ -11494,27 +11532,27 @@
       </c>
       <c r="E307" s="8" t="e"/>
       <c r="F307" s="9" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G307" s="9" t="e"/>
       <c r="H307" s="9" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="I307" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J307" s="10" t="n">
-        <v>7.2</v>
+        <v>31.68</v>
       </c>
       <c r="K307" s="11" t="e"/>
       <c r="L307" s="11" t="e"/>
       <c r="M307" s="10" t="n">
-        <v>7.2</v>
+        <v>31.68</v>
       </c>
       <c r="N307" s="11" t="e"/>
       <c r="O307" s="11" t="e"/>
       <c r="P307" s="10" t="n">
-        <v>7.2</v>
+        <v>31.68</v>
       </c>
       <c r="Q307" s="12" t="e"/>
     </row>
@@ -11529,27 +11567,27 @@
       </c>
       <c r="E308" s="8" t="e"/>
       <c r="F308" s="9" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="G308" s="9" t="e"/>
       <c r="H308" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I308" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J308" s="10" t="n">
-        <v>7.2</v>
+        <v>1.44</v>
       </c>
       <c r="K308" s="11" t="e"/>
       <c r="L308" s="11" t="e"/>
       <c r="M308" s="10" t="n">
-        <v>7.2</v>
+        <v>1.44</v>
       </c>
       <c r="N308" s="11" t="e"/>
       <c r="O308" s="11" t="e"/>
       <c r="P308" s="10" t="n">
-        <v>7.2</v>
+        <v>1.44</v>
       </c>
       <c r="Q308" s="12" t="e"/>
     </row>
@@ -11564,33 +11602,33 @@
       </c>
       <c r="E309" s="8" t="e"/>
       <c r="F309" s="9" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="G309" s="9" t="e"/>
       <c r="H309" s="9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I309" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J309" s="10" t="n">
-        <v>5.04</v>
+        <v>7.92</v>
       </c>
       <c r="K309" s="11" t="e"/>
       <c r="L309" s="11" t="e"/>
       <c r="M309" s="10" t="n">
-        <v>5.04</v>
+        <v>7.92</v>
       </c>
       <c r="N309" s="11" t="e"/>
       <c r="O309" s="11" t="e"/>
       <c r="P309" s="10" t="n">
-        <v>5.04</v>
+        <v>7.92</v>
       </c>
       <c r="Q309" s="12" t="e"/>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="1">
       <c r="A310" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B310" s="7" t="e"/>
       <c r="C310" s="7" t="e"/>
@@ -11599,450 +11637,450 @@
       </c>
       <c r="E310" s="8" t="e"/>
       <c r="F310" s="9" t="s">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="G310" s="9" t="e"/>
       <c r="H310" s="9" t="s">
-        <v>252</v>
+        <v>167</v>
       </c>
       <c r="I310" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J310" s="10" t="n">
-        <v>57.96</v>
+        <v>45.36</v>
       </c>
       <c r="K310" s="11" t="e"/>
       <c r="L310" s="11" t="e"/>
       <c r="M310" s="10" t="n">
-        <v>57.96</v>
+        <v>45.36</v>
       </c>
       <c r="N310" s="11" t="e"/>
       <c r="O310" s="11" t="e"/>
       <c r="P310" s="10" t="n">
-        <v>57.96</v>
+        <v>45.36</v>
       </c>
       <c r="Q310" s="12" t="e"/>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A311" s="13" t="e"/>
-      <c r="B311" s="14" t="e"/>
-      <c r="C311" s="15" t="e"/>
-      <c r="D311" s="16" t="e"/>
-      <c r="E311" s="17" t="e"/>
+      <c r="A311" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B311" s="7" t="e"/>
+      <c r="C311" s="7" t="e"/>
+      <c r="D311" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E311" s="8" t="e"/>
       <c r="F311" s="9" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="G311" s="9" t="e"/>
       <c r="H311" s="9" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I311" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J311" s="10" t="n">
-        <v>1</v>
+        <v>41.04</v>
       </c>
       <c r="K311" s="11" t="e"/>
       <c r="L311" s="11" t="e"/>
       <c r="M311" s="10" t="n">
-        <v>1</v>
+        <v>41.04</v>
       </c>
       <c r="N311" s="11" t="e"/>
       <c r="O311" s="11" t="e"/>
       <c r="P311" s="10" t="n">
-        <v>1</v>
+        <v>41.04</v>
       </c>
       <c r="Q311" s="12" t="e"/>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A312" s="13" t="e"/>
-      <c r="B312" s="14" t="e"/>
-      <c r="C312" s="15" t="e"/>
-      <c r="D312" s="16" t="e"/>
-      <c r="E312" s="17" t="e"/>
+      <c r="A312" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B312" s="7" t="e"/>
+      <c r="C312" s="7" t="e"/>
+      <c r="D312" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E312" s="8" t="e"/>
       <c r="F312" s="9" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="G312" s="9" t="e"/>
       <c r="H312" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I312" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J312" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="K312" s="11" t="e"/>
       <c r="L312" s="11" t="e"/>
       <c r="M312" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="N312" s="11" t="e"/>
       <c r="O312" s="11" t="e"/>
       <c r="P312" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="Q312" s="12" t="e"/>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A313" s="13" t="e"/>
-      <c r="B313" s="14" t="e"/>
-      <c r="C313" s="15" t="e"/>
-      <c r="D313" s="16" t="e"/>
-      <c r="E313" s="17" t="e"/>
+      <c r="A313" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B313" s="7" t="e"/>
+      <c r="C313" s="7" t="e"/>
+      <c r="D313" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E313" s="8" t="e"/>
       <c r="F313" s="9" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="G313" s="9" t="e"/>
       <c r="H313" s="9" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="I313" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J313" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="K313" s="11" t="e"/>
       <c r="L313" s="11" t="e"/>
       <c r="M313" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="N313" s="11" t="e"/>
       <c r="O313" s="11" t="e"/>
       <c r="P313" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="Q313" s="12" t="e"/>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A314" s="13" t="e"/>
-      <c r="B314" s="14" t="e"/>
-      <c r="C314" s="15" t="e"/>
-      <c r="D314" s="16" t="e"/>
-      <c r="E314" s="17" t="e"/>
+      <c r="A314" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B314" s="7" t="e"/>
+      <c r="C314" s="7" t="e"/>
+      <c r="D314" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E314" s="8" t="e"/>
       <c r="F314" s="9" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G314" s="9" t="e"/>
       <c r="H314" s="9" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I314" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J314" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="K314" s="11" t="e"/>
       <c r="L314" s="11" t="e"/>
       <c r="M314" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="N314" s="11" t="e"/>
       <c r="O314" s="11" t="e"/>
       <c r="P314" s="10" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="Q314" s="12" t="e"/>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A315" s="13" t="e"/>
-      <c r="B315" s="14" t="e"/>
-      <c r="C315" s="15" t="e"/>
-      <c r="D315" s="16" t="e"/>
-      <c r="E315" s="17" t="e"/>
+      <c r="A315" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" s="7" t="e"/>
+      <c r="C315" s="7" t="e"/>
+      <c r="D315" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E315" s="8" t="e"/>
       <c r="F315" s="9" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G315" s="9" t="e"/>
       <c r="H315" s="9" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="I315" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J315" s="10" t="n">
-        <v>1</v>
+        <v>5.04</v>
       </c>
       <c r="K315" s="11" t="e"/>
       <c r="L315" s="11" t="e"/>
       <c r="M315" s="10" t="n">
-        <v>1</v>
+        <v>5.04</v>
       </c>
       <c r="N315" s="11" t="e"/>
       <c r="O315" s="11" t="e"/>
       <c r="P315" s="10" t="n">
-        <v>1</v>
+        <v>5.04</v>
       </c>
       <c r="Q315" s="12" t="e"/>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A316" s="13" t="e"/>
-      <c r="B316" s="14" t="e"/>
-      <c r="C316" s="15" t="e"/>
-      <c r="D316" s="16" t="e"/>
-      <c r="E316" s="17" t="e"/>
+      <c r="A316" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B316" s="7" t="e"/>
+      <c r="C316" s="7" t="e"/>
+      <c r="D316" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E316" s="8" t="e"/>
       <c r="F316" s="9" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="G316" s="9" t="e"/>
       <c r="H316" s="9" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J316" s="10" t="n">
-        <v>1</v>
+        <v>57.96</v>
       </c>
       <c r="K316" s="11" t="e"/>
       <c r="L316" s="11" t="e"/>
       <c r="M316" s="10" t="n">
-        <v>1</v>
+        <v>57.96</v>
       </c>
       <c r="N316" s="11" t="e"/>
       <c r="O316" s="11" t="e"/>
       <c r="P316" s="10" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="Q316" s="12" t="e"/>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A317" s="13" t="e"/>
+      <c r="B317" s="14" t="e"/>
+      <c r="C317" s="15" t="e"/>
+      <c r="D317" s="16" t="e"/>
+      <c r="E317" s="17" t="e"/>
+      <c r="F317" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G317" s="9" t="e"/>
+      <c r="H317" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I317" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J317" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q316" s="12" t="e"/>
-    </row>
-    <row r="317" ht="11" customHeight="true">
-      <c r="A317" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B317" s="5" t="e"/>
-      <c r="C317" s="5" t="e"/>
-      <c r="D317" s="5" t="e"/>
-      <c r="E317" s="5" t="e"/>
-      <c r="F317" s="5" t="e"/>
-      <c r="G317" s="5" t="e"/>
-      <c r="H317" s="5" t="e"/>
-      <c r="I317" s="5" t="e"/>
-      <c r="J317" s="6" t="e"/>
-      <c r="K317" s="6" t="e"/>
-      <c r="L317" s="6" t="e"/>
-      <c r="M317" s="6" t="e"/>
-      <c r="N317" s="6" t="e"/>
-      <c r="O317" s="6" t="e"/>
-      <c r="P317" s="6" t="e"/>
-      <c r="Q317" s="6" t="e"/>
+      <c r="K317" s="11" t="e"/>
+      <c r="L317" s="11" t="e"/>
+      <c r="M317" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N317" s="11" t="e"/>
+      <c r="O317" s="11" t="e"/>
+      <c r="P317" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q317" s="12" t="e"/>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A318" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B318" s="7" t="e"/>
-      <c r="C318" s="7" t="e"/>
-      <c r="D318" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E318" s="8" t="e"/>
+      <c r="A318" s="13" t="e"/>
+      <c r="B318" s="14" t="e"/>
+      <c r="C318" s="15" t="e"/>
+      <c r="D318" s="16" t="e"/>
+      <c r="E318" s="17" t="e"/>
       <c r="F318" s="9" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="G318" s="9" t="e"/>
       <c r="H318" s="9" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="I318" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J318" s="10" t="n">
-        <v>7.56</v>
+        <v>1</v>
       </c>
       <c r="K318" s="11" t="e"/>
       <c r="L318" s="11" t="e"/>
       <c r="M318" s="10" t="n">
-        <v>7.56</v>
+        <v>1</v>
       </c>
       <c r="N318" s="11" t="e"/>
       <c r="O318" s="11" t="e"/>
       <c r="P318" s="10" t="n">
-        <v>7.56</v>
+        <v>1</v>
       </c>
       <c r="Q318" s="12" t="e"/>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A319" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B319" s="7" t="e"/>
-      <c r="C319" s="7" t="e"/>
-      <c r="D319" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E319" s="8" t="e"/>
+      <c r="A319" s="13" t="e"/>
+      <c r="B319" s="14" t="e"/>
+      <c r="C319" s="15" t="e"/>
+      <c r="D319" s="16" t="e"/>
+      <c r="E319" s="17" t="e"/>
       <c r="F319" s="9" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="G319" s="9" t="e"/>
       <c r="H319" s="9" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="I319" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J319" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="K319" s="11" t="e"/>
       <c r="L319" s="11" t="e"/>
       <c r="M319" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="N319" s="11" t="e"/>
       <c r="O319" s="11" t="e"/>
       <c r="P319" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="Q319" s="12" t="e"/>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A320" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B320" s="7" t="e"/>
-      <c r="C320" s="7" t="e"/>
-      <c r="D320" s="8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E320" s="8" t="e"/>
+      <c r="A320" s="13" t="e"/>
+      <c r="B320" s="14" t="e"/>
+      <c r="C320" s="15" t="e"/>
+      <c r="D320" s="16" t="e"/>
+      <c r="E320" s="17" t="e"/>
       <c r="F320" s="9" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G320" s="9" t="e"/>
       <c r="H320" s="9" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="I320" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J320" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="K320" s="11" t="e"/>
       <c r="L320" s="11" t="e"/>
       <c r="M320" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="N320" s="11" t="e"/>
       <c r="O320" s="11" t="e"/>
       <c r="P320" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="Q320" s="12" t="e"/>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A321" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B321" s="7" t="e"/>
-      <c r="C321" s="7" t="e"/>
-      <c r="D321" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E321" s="8" t="e"/>
+      <c r="A321" s="13" t="e"/>
+      <c r="B321" s="14" t="e"/>
+      <c r="C321" s="15" t="e"/>
+      <c r="D321" s="16" t="e"/>
+      <c r="E321" s="17" t="e"/>
       <c r="F321" s="9" t="s">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="G321" s="9" t="e"/>
       <c r="H321" s="9" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="I321" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J321" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="K321" s="11" t="e"/>
       <c r="L321" s="11" t="e"/>
       <c r="M321" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="N321" s="11" t="e"/>
       <c r="O321" s="11" t="e"/>
       <c r="P321" s="10" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="Q321" s="12" t="e"/>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A322" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B322" s="7" t="e"/>
-      <c r="C322" s="7" t="e"/>
-      <c r="D322" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E322" s="8" t="e"/>
+      <c r="A322" s="13" t="e"/>
+      <c r="B322" s="14" t="e"/>
+      <c r="C322" s="15" t="e"/>
+      <c r="D322" s="16" t="e"/>
+      <c r="E322" s="17" t="e"/>
       <c r="F322" s="9" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="G322" s="9" t="e"/>
       <c r="H322" s="9" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="I322" s="9" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J322" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="K322" s="11" t="e"/>
       <c r="L322" s="11" t="e"/>
       <c r="M322" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="N322" s="11" t="e"/>
       <c r="O322" s="11" t="e"/>
       <c r="P322" s="10" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="Q322" s="12" t="e"/>
     </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A323" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B323" s="7" t="e"/>
-      <c r="C323" s="7" t="e"/>
-      <c r="D323" s="8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E323" s="8" t="e"/>
-      <c r="F323" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G323" s="9" t="e"/>
-      <c r="H323" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I323" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J323" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K323" s="11" t="e"/>
-      <c r="L323" s="11" t="e"/>
-      <c r="M323" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N323" s="11" t="e"/>
-      <c r="O323" s="11" t="e"/>
-      <c r="P323" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q323" s="12" t="e"/>
+    <row r="323" ht="11" customHeight="true">
+      <c r="A323" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B323" s="5" t="e"/>
+      <c r="C323" s="5" t="e"/>
+      <c r="D323" s="5" t="e"/>
+      <c r="E323" s="5" t="e"/>
+      <c r="F323" s="5" t="e"/>
+      <c r="G323" s="5" t="e"/>
+      <c r="H323" s="5" t="e"/>
+      <c r="I323" s="5" t="e"/>
+      <c r="J323" s="6" t="e"/>
+      <c r="K323" s="6" t="e"/>
+      <c r="L323" s="6" t="e"/>
+      <c r="M323" s="6" t="e"/>
+      <c r="N323" s="6" t="e"/>
+      <c r="O323" s="6" t="e"/>
+      <c r="P323" s="6" t="e"/>
+      <c r="Q323" s="6" t="e"/>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="1">
       <c r="A324" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B324" s="7" t="e"/>
       <c r="C324" s="7" t="e"/>
@@ -12051,27 +12089,27 @@
       </c>
       <c r="E324" s="8" t="e"/>
       <c r="F324" s="9" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G324" s="9" t="e"/>
       <c r="H324" s="9" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="I324" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J324" s="10" t="n">
-        <v>1.44</v>
+        <v>7.56</v>
       </c>
       <c r="K324" s="11" t="e"/>
       <c r="L324" s="11" t="e"/>
       <c r="M324" s="10" t="n">
-        <v>1.44</v>
+        <v>7.56</v>
       </c>
       <c r="N324" s="11" t="e"/>
       <c r="O324" s="11" t="e"/>
       <c r="P324" s="10" t="n">
-        <v>1.44</v>
+        <v>7.56</v>
       </c>
       <c r="Q324" s="12" t="e"/>
     </row>
@@ -12086,11 +12124,11 @@
       </c>
       <c r="E325" s="8" t="e"/>
       <c r="F325" s="9" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G325" s="9" t="e"/>
       <c r="H325" s="9" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="I325" s="9" t="s">
         <v>22</v>
@@ -12112,36 +12150,36 @@
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="1">
       <c r="A326" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B326" s="7" t="e"/>
       <c r="C326" s="7" t="e"/>
       <c r="D326" s="8" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="E326" s="8" t="e"/>
       <c r="F326" s="9" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="G326" s="9" t="e"/>
       <c r="H326" s="9" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="I326" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J326" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K326" s="11" t="e"/>
       <c r="L326" s="11" t="e"/>
       <c r="M326" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N326" s="11" t="e"/>
       <c r="O326" s="11" t="e"/>
       <c r="P326" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q326" s="12" t="e"/>
     </row>
@@ -12156,11 +12194,11 @@
       </c>
       <c r="E327" s="8" t="e"/>
       <c r="F327" s="9" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G327" s="9" t="e"/>
       <c r="H327" s="9" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="I327" s="9" t="s">
         <v>22</v>
@@ -12191,33 +12229,33 @@
       </c>
       <c r="E328" s="8" t="e"/>
       <c r="F328" s="9" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G328" s="9" t="e"/>
       <c r="H328" s="9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="I328" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J328" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K328" s="11" t="e"/>
       <c r="L328" s="11" t="e"/>
       <c r="M328" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N328" s="11" t="e"/>
       <c r="O328" s="11" t="e"/>
       <c r="P328" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q328" s="12" t="e"/>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="1">
       <c r="A329" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B329" s="7" t="e"/>
       <c r="C329" s="7" t="e"/>
@@ -12226,27 +12264,27 @@
       </c>
       <c r="E329" s="8" t="e"/>
       <c r="F329" s="9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G329" s="9" t="e"/>
       <c r="H329" s="9" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I329" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J329" s="10" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="K329" s="11" t="e"/>
       <c r="L329" s="11" t="e"/>
       <c r="M329" s="10" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="N329" s="11" t="e"/>
       <c r="O329" s="11" t="e"/>
       <c r="P329" s="10" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q329" s="12" t="e"/>
     </row>
@@ -12261,11 +12299,11 @@
       </c>
       <c r="E330" s="8" t="e"/>
       <c r="F330" s="9" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G330" s="9" t="e"/>
       <c r="H330" s="9" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="I330" s="9" t="s">
         <v>22</v>
@@ -12296,27 +12334,27 @@
       </c>
       <c r="E331" s="8" t="e"/>
       <c r="F331" s="9" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G331" s="9" t="e"/>
       <c r="H331" s="9" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="I331" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J331" s="10" t="n">
-        <v>2.88</v>
+        <v>0.72</v>
       </c>
       <c r="K331" s="11" t="e"/>
       <c r="L331" s="11" t="e"/>
       <c r="M331" s="10" t="n">
-        <v>2.88</v>
+        <v>0.72</v>
       </c>
       <c r="N331" s="11" t="e"/>
       <c r="O331" s="11" t="e"/>
       <c r="P331" s="10" t="n">
-        <v>2.88</v>
+        <v>0.72</v>
       </c>
       <c r="Q331" s="12" t="e"/>
     </row>
@@ -12331,27 +12369,27 @@
       </c>
       <c r="E332" s="8" t="e"/>
       <c r="F332" s="9" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="G332" s="9" t="e"/>
       <c r="H332" s="9" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I332" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J332" s="10" t="n">
-        <v>6.48</v>
+        <v>0.72</v>
       </c>
       <c r="K332" s="11" t="e"/>
       <c r="L332" s="11" t="e"/>
       <c r="M332" s="10" t="n">
-        <v>6.48</v>
+        <v>0.72</v>
       </c>
       <c r="N332" s="11" t="e"/>
       <c r="O332" s="11" t="e"/>
       <c r="P332" s="10" t="n">
-        <v>6.48</v>
+        <v>0.72</v>
       </c>
       <c r="Q332" s="12" t="e"/>
     </row>
@@ -12366,27 +12404,27 @@
       </c>
       <c r="E333" s="8" t="e"/>
       <c r="F333" s="9" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G333" s="9" t="e"/>
       <c r="H333" s="9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I333" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J333" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="K333" s="11" t="e"/>
       <c r="L333" s="11" t="e"/>
       <c r="M333" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="N333" s="11" t="e"/>
       <c r="O333" s="11" t="e"/>
       <c r="P333" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="Q333" s="12" t="e"/>
     </row>
@@ -12401,11 +12439,11 @@
       </c>
       <c r="E334" s="8" t="e"/>
       <c r="F334" s="9" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="G334" s="9" t="e"/>
       <c r="H334" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="I334" s="9" t="s">
         <v>22</v>
@@ -12427,7 +12465,7 @@
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="1">
       <c r="A335" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B335" s="7" t="e"/>
       <c r="C335" s="7" t="e"/>
@@ -12436,27 +12474,27 @@
       </c>
       <c r="E335" s="8" t="e"/>
       <c r="F335" s="9" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="G335" s="9" t="e"/>
       <c r="H335" s="9" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="I335" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J335" s="10" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="K335" s="11" t="e"/>
       <c r="L335" s="11" t="e"/>
       <c r="M335" s="10" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="N335" s="11" t="e"/>
       <c r="O335" s="11" t="e"/>
       <c r="P335" s="10" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="Q335" s="12" t="e"/>
     </row>
@@ -12471,11 +12509,11 @@
       </c>
       <c r="E336" s="8" t="e"/>
       <c r="F336" s="9" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="G336" s="9" t="e"/>
       <c r="H336" s="9" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="I336" s="9" t="s">
         <v>22</v>
@@ -12506,33 +12544,33 @@
       </c>
       <c r="E337" s="8" t="e"/>
       <c r="F337" s="9" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="G337" s="9" t="e"/>
       <c r="H337" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I337" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J337" s="10" t="n">
-        <v>0.72</v>
+        <v>2.88</v>
       </c>
       <c r="K337" s="11" t="e"/>
       <c r="L337" s="11" t="e"/>
       <c r="M337" s="10" t="n">
-        <v>0.72</v>
+        <v>2.88</v>
       </c>
       <c r="N337" s="11" t="e"/>
       <c r="O337" s="11" t="e"/>
       <c r="P337" s="10" t="n">
-        <v>0.72</v>
+        <v>2.88</v>
       </c>
       <c r="Q337" s="12" t="e"/>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="1">
       <c r="A338" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B338" s="7" t="e"/>
       <c r="C338" s="7" t="e"/>
@@ -12541,33 +12579,33 @@
       </c>
       <c r="E338" s="8" t="e"/>
       <c r="F338" s="9" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="G338" s="9" t="e"/>
       <c r="H338" s="9" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="I338" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J338" s="10" t="n">
-        <v>11.88</v>
+        <v>6.48</v>
       </c>
       <c r="K338" s="11" t="e"/>
       <c r="L338" s="11" t="e"/>
       <c r="M338" s="10" t="n">
-        <v>11.88</v>
+        <v>6.48</v>
       </c>
       <c r="N338" s="11" t="e"/>
       <c r="O338" s="11" t="e"/>
       <c r="P338" s="10" t="n">
-        <v>11.88</v>
+        <v>6.48</v>
       </c>
       <c r="Q338" s="12" t="e"/>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="1">
       <c r="A339" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B339" s="7" t="e"/>
       <c r="C339" s="7" t="e"/>
@@ -12576,27 +12614,27 @@
       </c>
       <c r="E339" s="8" t="e"/>
       <c r="F339" s="9" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="G339" s="9" t="e"/>
       <c r="H339" s="9" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="I339" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J339" s="10" t="n">
-        <v>57.6</v>
+        <v>1.44</v>
       </c>
       <c r="K339" s="11" t="e"/>
       <c r="L339" s="11" t="e"/>
       <c r="M339" s="10" t="n">
-        <v>57.6</v>
+        <v>1.44</v>
       </c>
       <c r="N339" s="11" t="e"/>
       <c r="O339" s="11" t="e"/>
       <c r="P339" s="10" t="n">
-        <v>57.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q339" s="12" t="e"/>
     </row>
@@ -12611,11 +12649,11 @@
       </c>
       <c r="E340" s="8" t="e"/>
       <c r="F340" s="9" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G340" s="9" t="e"/>
       <c r="H340" s="9" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="I340" s="9" t="s">
         <v>22</v>
@@ -12646,27 +12684,27 @@
       </c>
       <c r="E341" s="8" t="e"/>
       <c r="F341" s="9" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="G341" s="9" t="e"/>
       <c r="H341" s="9" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I341" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J341" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K341" s="11" t="e"/>
       <c r="L341" s="11" t="e"/>
       <c r="M341" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N341" s="11" t="e"/>
       <c r="O341" s="11" t="e"/>
       <c r="P341" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q341" s="12" t="e"/>
     </row>
@@ -12681,27 +12719,27 @@
       </c>
       <c r="E342" s="8" t="e"/>
       <c r="F342" s="9" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G342" s="9" t="e"/>
       <c r="H342" s="9" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I342" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J342" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K342" s="11" t="e"/>
       <c r="L342" s="11" t="e"/>
       <c r="M342" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N342" s="11" t="e"/>
       <c r="O342" s="11" t="e"/>
       <c r="P342" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q342" s="12" t="e"/>
     </row>
@@ -12716,33 +12754,33 @@
       </c>
       <c r="E343" s="8" t="e"/>
       <c r="F343" s="9" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="G343" s="9" t="e"/>
       <c r="H343" s="9" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="I343" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J343" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="K343" s="11" t="e"/>
       <c r="L343" s="11" t="e"/>
       <c r="M343" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="N343" s="11" t="e"/>
       <c r="O343" s="11" t="e"/>
       <c r="P343" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="Q343" s="12" t="e"/>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="1">
       <c r="A344" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B344" s="7" t="e"/>
       <c r="C344" s="7" t="e"/>
@@ -12751,33 +12789,33 @@
       </c>
       <c r="E344" s="8" t="e"/>
       <c r="F344" s="9" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="G344" s="9" t="e"/>
       <c r="H344" s="9" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="I344" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J344" s="10" t="n">
-        <v>1.44</v>
+        <v>11.88</v>
       </c>
       <c r="K344" s="11" t="e"/>
       <c r="L344" s="11" t="e"/>
       <c r="M344" s="10" t="n">
-        <v>1.44</v>
+        <v>11.88</v>
       </c>
       <c r="N344" s="11" t="e"/>
       <c r="O344" s="11" t="e"/>
       <c r="P344" s="10" t="n">
-        <v>1.44</v>
+        <v>11.88</v>
       </c>
       <c r="Q344" s="12" t="e"/>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="1">
       <c r="A345" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B345" s="7" t="e"/>
       <c r="C345" s="7" t="e"/>
@@ -12786,33 +12824,33 @@
       </c>
       <c r="E345" s="8" t="e"/>
       <c r="F345" s="9" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="G345" s="9" t="e"/>
       <c r="H345" s="9" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="I345" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J345" s="10" t="n">
-        <v>0.72</v>
+        <v>57.6</v>
       </c>
       <c r="K345" s="11" t="e"/>
       <c r="L345" s="11" t="e"/>
       <c r="M345" s="10" t="n">
-        <v>0.72</v>
+        <v>57.6</v>
       </c>
       <c r="N345" s="11" t="e"/>
       <c r="O345" s="11" t="e"/>
       <c r="P345" s="10" t="n">
-        <v>0.72</v>
+        <v>57.6</v>
       </c>
       <c r="Q345" s="12" t="e"/>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="1">
       <c r="A346" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B346" s="7" t="e"/>
       <c r="C346" s="7" t="e"/>
@@ -12821,27 +12859,27 @@
       </c>
       <c r="E346" s="8" t="e"/>
       <c r="F346" s="9" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="G346" s="9" t="e"/>
       <c r="H346" s="9" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="I346" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J346" s="10" t="n">
-        <v>57.6</v>
+        <v>0.72</v>
       </c>
       <c r="K346" s="11" t="e"/>
       <c r="L346" s="11" t="e"/>
       <c r="M346" s="10" t="n">
-        <v>57.6</v>
+        <v>0.72</v>
       </c>
       <c r="N346" s="11" t="e"/>
       <c r="O346" s="11" t="e"/>
       <c r="P346" s="10" t="n">
-        <v>57.6</v>
+        <v>0.72</v>
       </c>
       <c r="Q346" s="12" t="e"/>
     </row>
@@ -12856,27 +12894,27 @@
       </c>
       <c r="E347" s="8" t="e"/>
       <c r="F347" s="9" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G347" s="9" t="e"/>
       <c r="H347" s="9" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="I347" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J347" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="K347" s="11" t="e"/>
       <c r="L347" s="11" t="e"/>
       <c r="M347" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="N347" s="11" t="e"/>
       <c r="O347" s="11" t="e"/>
       <c r="P347" s="10" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="Q347" s="12" t="e"/>
     </row>
@@ -12891,11 +12929,11 @@
       </c>
       <c r="E348" s="8" t="e"/>
       <c r="F348" s="9" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G348" s="9" t="e"/>
       <c r="H348" s="9" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I348" s="9" t="s">
         <v>22</v>
@@ -12926,11 +12964,11 @@
       </c>
       <c r="E349" s="8" t="e"/>
       <c r="F349" s="9" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="G349" s="9" t="e"/>
       <c r="H349" s="9" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="I349" s="9" t="s">
         <v>22</v>
@@ -12961,27 +12999,27 @@
       </c>
       <c r="E350" s="8" t="e"/>
       <c r="F350" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G350" s="9" t="e"/>
       <c r="H350" s="9" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="I350" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J350" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K350" s="11" t="e"/>
       <c r="L350" s="11" t="e"/>
       <c r="M350" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N350" s="11" t="e"/>
       <c r="O350" s="11" t="e"/>
       <c r="P350" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q350" s="12" t="e"/>
     </row>
@@ -12996,11 +13034,11 @@
       </c>
       <c r="E351" s="8" t="e"/>
       <c r="F351" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G351" s="9" t="e"/>
       <c r="H351" s="9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I351" s="9" t="s">
         <v>22</v>
@@ -13022,7 +13060,7 @@
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="1">
       <c r="A352" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B352" s="7" t="e"/>
       <c r="C352" s="7" t="e"/>
@@ -13031,27 +13069,27 @@
       </c>
       <c r="E352" s="8" t="e"/>
       <c r="F352" s="9" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="G352" s="9" t="e"/>
       <c r="H352" s="9" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="I352" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J352" s="10" t="n">
-        <v>1.44</v>
+        <v>57.6</v>
       </c>
       <c r="K352" s="11" t="e"/>
       <c r="L352" s="11" t="e"/>
       <c r="M352" s="10" t="n">
-        <v>1.44</v>
+        <v>57.6</v>
       </c>
       <c r="N352" s="11" t="e"/>
       <c r="O352" s="11" t="e"/>
       <c r="P352" s="10" t="n">
-        <v>1.44</v>
+        <v>57.6</v>
       </c>
       <c r="Q352" s="12" t="e"/>
     </row>
@@ -13066,27 +13104,27 @@
       </c>
       <c r="E353" s="8" t="e"/>
       <c r="F353" s="9" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G353" s="9" t="e"/>
       <c r="H353" s="9" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I353" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J353" s="10" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="K353" s="11" t="e"/>
       <c r="L353" s="11" t="e"/>
       <c r="M353" s="10" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="N353" s="11" t="e"/>
       <c r="O353" s="11" t="e"/>
       <c r="P353" s="10" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="Q353" s="12" t="e"/>
     </row>
@@ -13101,29 +13139,25 @@
       </c>
       <c r="E354" s="8" t="e"/>
       <c r="F354" s="9" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G354" s="9" t="e"/>
       <c r="H354" s="9" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I354" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J354" s="10" t="n">
-        <v>83.52</v>
+        <v>0.72</v>
       </c>
       <c r="K354" s="11" t="e"/>
-      <c r="L354" s="10" t="n">
-        <v>82.8</v>
-      </c>
+      <c r="L354" s="11" t="e"/>
       <c r="M354" s="10" t="n">
         <v>0.72</v>
       </c>
       <c r="N354" s="11" t="e"/>
-      <c r="O354" s="10" t="n">
-        <v>82.8</v>
-      </c>
+      <c r="O354" s="11" t="e"/>
       <c r="P354" s="10" t="n">
         <v>0.72</v>
       </c>
@@ -13140,11 +13174,11 @@
       </c>
       <c r="E355" s="8" t="e"/>
       <c r="F355" s="9" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G355" s="9" t="e"/>
       <c r="H355" s="9" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="I355" s="9" t="s">
         <v>22</v>
@@ -13175,11 +13209,11 @@
       </c>
       <c r="E356" s="8" t="e"/>
       <c r="F356" s="9" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G356" s="9" t="e"/>
       <c r="H356" s="9" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="I356" s="9" t="s">
         <v>22</v>
@@ -13210,11 +13244,11 @@
       </c>
       <c r="E357" s="8" t="e"/>
       <c r="F357" s="9" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="G357" s="9" t="e"/>
       <c r="H357" s="9" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I357" s="9" t="s">
         <v>22</v>
@@ -13245,27 +13279,27 @@
       </c>
       <c r="E358" s="8" t="e"/>
       <c r="F358" s="9" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="G358" s="9" t="e"/>
       <c r="H358" s="9" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="I358" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J358" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K358" s="11" t="e"/>
       <c r="L358" s="11" t="e"/>
       <c r="M358" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N358" s="11" t="e"/>
       <c r="O358" s="11" t="e"/>
       <c r="P358" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q358" s="12" t="e"/>
     </row>
@@ -13280,27 +13314,27 @@
       </c>
       <c r="E359" s="8" t="e"/>
       <c r="F359" s="9" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="G359" s="9" t="e"/>
       <c r="H359" s="9" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="I359" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J359" s="10" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="K359" s="11" t="e"/>
       <c r="L359" s="11" t="e"/>
       <c r="M359" s="10" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="N359" s="11" t="e"/>
       <c r="O359" s="11" t="e"/>
       <c r="P359" s="10" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q359" s="12" t="e"/>
     </row>
@@ -13315,25 +13349,29 @@
       </c>
       <c r="E360" s="8" t="e"/>
       <c r="F360" s="9" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G360" s="9" t="e"/>
       <c r="H360" s="9" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I360" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J360" s="10" t="n">
-        <v>0.72</v>
+        <v>83.52</v>
       </c>
       <c r="K360" s="11" t="e"/>
-      <c r="L360" s="11" t="e"/>
+      <c r="L360" s="10" t="n">
+        <v>82.8</v>
+      </c>
       <c r="M360" s="10" t="n">
         <v>0.72</v>
       </c>
       <c r="N360" s="11" t="e"/>
-      <c r="O360" s="11" t="e"/>
+      <c r="O360" s="10" t="n">
+        <v>82.8</v>
+      </c>
       <c r="P360" s="10" t="n">
         <v>0.72</v>
       </c>
@@ -13350,115 +13388,325 @@
       </c>
       <c r="E361" s="8" t="e"/>
       <c r="F361" s="9" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G361" s="9" t="e"/>
       <c r="H361" s="9" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I361" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J361" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="K361" s="11" t="e"/>
       <c r="L361" s="11" t="e"/>
       <c r="M361" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N361" s="11" t="e"/>
       <c r="O361" s="11" t="e"/>
       <c r="P361" s="10" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="Q361" s="12" t="e"/>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A362" s="13" t="e"/>
-      <c r="B362" s="14" t="e"/>
-      <c r="C362" s="15" t="e"/>
-      <c r="D362" s="16" t="e"/>
-      <c r="E362" s="17" t="e"/>
+      <c r="A362" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B362" s="7" t="e"/>
+      <c r="C362" s="7" t="e"/>
+      <c r="D362" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E362" s="8" t="e"/>
       <c r="F362" s="9" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="G362" s="9" t="e"/>
       <c r="H362" s="9" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="I362" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J362" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="K362" s="11" t="e"/>
       <c r="L362" s="11" t="e"/>
       <c r="M362" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="N362" s="11" t="e"/>
       <c r="O362" s="11" t="e"/>
       <c r="P362" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="Q362" s="12" t="e"/>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A363" s="13" t="e"/>
-      <c r="B363" s="14" t="e"/>
-      <c r="C363" s="15" t="e"/>
-      <c r="D363" s="16" t="e"/>
-      <c r="E363" s="17" t="e"/>
+      <c r="A363" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B363" s="7" t="e"/>
+      <c r="C363" s="7" t="e"/>
+      <c r="D363" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E363" s="8" t="e"/>
       <c r="F363" s="9" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="G363" s="9" t="e"/>
       <c r="H363" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I363" s="9" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="J363" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="K363" s="11" t="e"/>
       <c r="L363" s="11" t="e"/>
       <c r="M363" s="10" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="N363" s="11" t="e"/>
       <c r="O363" s="11" t="e"/>
       <c r="P363" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q363" s="12" t="e"/>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A364" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B364" s="7" t="e"/>
+      <c r="C364" s="7" t="e"/>
+      <c r="D364" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E364" s="8" t="e"/>
+      <c r="F364" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G364" s="9" t="e"/>
+      <c r="H364" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I364" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J364" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K364" s="11" t="e"/>
+      <c r="L364" s="11" t="e"/>
+      <c r="M364" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N364" s="11" t="e"/>
+      <c r="O364" s="11" t="e"/>
+      <c r="P364" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q364" s="12" t="e"/>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A365" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B365" s="7" t="e"/>
+      <c r="C365" s="7" t="e"/>
+      <c r="D365" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E365" s="8" t="e"/>
+      <c r="F365" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G365" s="9" t="e"/>
+      <c r="H365" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I365" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J365" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K365" s="11" t="e"/>
+      <c r="L365" s="11" t="e"/>
+      <c r="M365" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N365" s="11" t="e"/>
+      <c r="O365" s="11" t="e"/>
+      <c r="P365" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q365" s="12" t="e"/>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A366" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B366" s="7" t="e"/>
+      <c r="C366" s="7" t="e"/>
+      <c r="D366" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E366" s="8" t="e"/>
+      <c r="F366" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G366" s="9" t="e"/>
+      <c r="H366" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I366" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J366" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K366" s="11" t="e"/>
+      <c r="L366" s="11" t="e"/>
+      <c r="M366" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N366" s="11" t="e"/>
+      <c r="O366" s="11" t="e"/>
+      <c r="P366" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q366" s="12" t="e"/>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A367" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B367" s="7" t="e"/>
+      <c r="C367" s="7" t="e"/>
+      <c r="D367" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E367" s="8" t="e"/>
+      <c r="F367" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G367" s="9" t="e"/>
+      <c r="H367" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I367" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J367" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K367" s="11" t="e"/>
+      <c r="L367" s="11" t="e"/>
+      <c r="M367" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N367" s="11" t="e"/>
+      <c r="O367" s="11" t="e"/>
+      <c r="P367" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q367" s="12" t="e"/>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A368" s="13" t="e"/>
+      <c r="B368" s="14" t="e"/>
+      <c r="C368" s="15" t="e"/>
+      <c r="D368" s="16" t="e"/>
+      <c r="E368" s="17" t="e"/>
+      <c r="F368" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G368" s="9" t="e"/>
+      <c r="H368" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I368" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J368" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q363" s="12" t="e"/>
-    </row>
-    <row r="364" ht="13" customHeight="true">
-      <c r="A364" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="B364" s="20" t="e"/>
-      <c r="C364" s="20" t="e"/>
-      <c r="D364" s="20" t="e"/>
-      <c r="E364" s="20" t="e"/>
-      <c r="F364" s="20" t="e"/>
-      <c r="G364" s="20" t="e"/>
-      <c r="H364" s="20" t="e"/>
-      <c r="I364" s="20" t="e"/>
-      <c r="J364" s="21" t="e"/>
-      <c r="K364" s="21" t="e"/>
-      <c r="L364" s="21" t="e"/>
-      <c r="M364" s="21" t="e"/>
-      <c r="N364" s="21" t="e"/>
-      <c r="O364" s="21" t="e"/>
-      <c r="P364" s="21" t="e"/>
-      <c r="Q364" s="21" t="e"/>
+      <c r="K368" s="11" t="e"/>
+      <c r="L368" s="11" t="e"/>
+      <c r="M368" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N368" s="11" t="e"/>
+      <c r="O368" s="11" t="e"/>
+      <c r="P368" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q368" s="12" t="e"/>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A369" s="13" t="e"/>
+      <c r="B369" s="14" t="e"/>
+      <c r="C369" s="15" t="e"/>
+      <c r="D369" s="16" t="e"/>
+      <c r="E369" s="17" t="e"/>
+      <c r="F369" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G369" s="9" t="e"/>
+      <c r="H369" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I369" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J369" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K369" s="11" t="e"/>
+      <c r="L369" s="11" t="e"/>
+      <c r="M369" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N369" s="11" t="e"/>
+      <c r="O369" s="11" t="e"/>
+      <c r="P369" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q369" s="12" t="e"/>
+    </row>
+    <row r="370" ht="13" customHeight="true">
+      <c r="A370" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B370" s="20" t="e"/>
+      <c r="C370" s="20" t="e"/>
+      <c r="D370" s="20" t="e"/>
+      <c r="E370" s="20" t="e"/>
+      <c r="F370" s="20" t="e"/>
+      <c r="G370" s="20" t="e"/>
+      <c r="H370" s="20" t="e"/>
+      <c r="I370" s="20" t="e"/>
+      <c r="J370" s="21" t="e"/>
+      <c r="K370" s="21" t="e"/>
+      <c r="L370" s="21" t="e"/>
+      <c r="M370" s="21" t="e"/>
+      <c r="N370" s="21" t="e"/>
+      <c r="O370" s="21" t="e"/>
+      <c r="P370" s="21" t="e"/>
+      <c r="Q370" s="21" t="e"/>
     </row>
   </sheetData>
-  <mergeCells count="927">
+  <mergeCells count="945">
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="J6:M6"/>
     <mergeCell ref="N6:P6"/>
@@ -14083,32 +14331,34 @@
     <mergeCell ref="A249:C249"/>
     <mergeCell ref="D249:E249"/>
     <mergeCell ref="F249:G249"/>
+    <mergeCell ref="A250:C250"/>
+    <mergeCell ref="D250:E250"/>
     <mergeCell ref="F250:G250"/>
+    <mergeCell ref="A251:C251"/>
+    <mergeCell ref="D251:E251"/>
     <mergeCell ref="F251:G251"/>
+    <mergeCell ref="A252:C252"/>
+    <mergeCell ref="D252:E252"/>
     <mergeCell ref="F252:G252"/>
+    <mergeCell ref="A253:C253"/>
+    <mergeCell ref="D253:E253"/>
     <mergeCell ref="F253:G253"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="D254:E254"/>
     <mergeCell ref="F254:G254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="D255:E255"/>
     <mergeCell ref="F255:G255"/>
     <mergeCell ref="F256:G256"/>
     <mergeCell ref="F257:G257"/>
     <mergeCell ref="F258:G258"/>
-    <mergeCell ref="A259:I259"/>
-    <mergeCell ref="A260:C260"/>
-    <mergeCell ref="D260:E260"/>
+    <mergeCell ref="F259:G259"/>
     <mergeCell ref="F260:G260"/>
-    <mergeCell ref="A261:C261"/>
-    <mergeCell ref="D261:E261"/>
     <mergeCell ref="F261:G261"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="D262:E262"/>
     <mergeCell ref="F262:G262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="D263:E263"/>
     <mergeCell ref="F263:G263"/>
     <mergeCell ref="F264:G264"/>
-    <mergeCell ref="A265:C265"/>
-    <mergeCell ref="D265:E265"/>
-    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="A265:I265"/>
     <mergeCell ref="A266:C266"/>
     <mergeCell ref="D266:E266"/>
     <mergeCell ref="F266:G266"/>
@@ -14121,8 +14371,6 @@
     <mergeCell ref="A269:C269"/>
     <mergeCell ref="D269:E269"/>
     <mergeCell ref="F269:G269"/>
-    <mergeCell ref="A270:C270"/>
-    <mergeCell ref="D270:E270"/>
     <mergeCell ref="F270:G270"/>
     <mergeCell ref="A271:C271"/>
     <mergeCell ref="D271:E271"/>
@@ -14244,31 +14492,31 @@
     <mergeCell ref="A310:C310"/>
     <mergeCell ref="D310:E310"/>
     <mergeCell ref="F310:G310"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="D311:E311"/>
     <mergeCell ref="F311:G311"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="D312:E312"/>
     <mergeCell ref="F312:G312"/>
+    <mergeCell ref="A313:C313"/>
+    <mergeCell ref="D313:E313"/>
     <mergeCell ref="F313:G313"/>
+    <mergeCell ref="A314:C314"/>
+    <mergeCell ref="D314:E314"/>
     <mergeCell ref="F314:G314"/>
+    <mergeCell ref="A315:C315"/>
+    <mergeCell ref="D315:E315"/>
     <mergeCell ref="F315:G315"/>
+    <mergeCell ref="A316:C316"/>
+    <mergeCell ref="D316:E316"/>
     <mergeCell ref="F316:G316"/>
-    <mergeCell ref="A317:I317"/>
-    <mergeCell ref="A318:C318"/>
-    <mergeCell ref="D318:E318"/>
+    <mergeCell ref="F317:G317"/>
     <mergeCell ref="F318:G318"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="D319:E319"/>
     <mergeCell ref="F319:G319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="D320:E320"/>
     <mergeCell ref="F320:G320"/>
-    <mergeCell ref="A321:C321"/>
-    <mergeCell ref="D321:E321"/>
     <mergeCell ref="F321:G321"/>
-    <mergeCell ref="A322:C322"/>
-    <mergeCell ref="D322:E322"/>
     <mergeCell ref="F322:G322"/>
-    <mergeCell ref="A323:C323"/>
-    <mergeCell ref="D323:E323"/>
-    <mergeCell ref="F323:G323"/>
+    <mergeCell ref="A323:I323"/>
     <mergeCell ref="A324:C324"/>
     <mergeCell ref="D324:E324"/>
     <mergeCell ref="F324:G324"/>
@@ -14383,9 +14631,27 @@
     <mergeCell ref="A361:C361"/>
     <mergeCell ref="D361:E361"/>
     <mergeCell ref="F361:G361"/>
+    <mergeCell ref="A362:C362"/>
+    <mergeCell ref="D362:E362"/>
     <mergeCell ref="F362:G362"/>
+    <mergeCell ref="A363:C363"/>
+    <mergeCell ref="D363:E363"/>
     <mergeCell ref="F363:G363"/>
-    <mergeCell ref="A364:I364"/>
+    <mergeCell ref="A364:C364"/>
+    <mergeCell ref="D364:E364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="A365:C365"/>
+    <mergeCell ref="D365:E365"/>
+    <mergeCell ref="F365:G365"/>
+    <mergeCell ref="A366:C366"/>
+    <mergeCell ref="D366:E366"/>
+    <mergeCell ref="F366:G366"/>
+    <mergeCell ref="A367:C367"/>
+    <mergeCell ref="D367:E367"/>
+    <mergeCell ref="F367:G367"/>
+    <mergeCell ref="F368:G368"/>
+    <mergeCell ref="F369:G369"/>
+    <mergeCell ref="A370:I370"/>
   </mergeCells>
   <pageMargins left="0.75" top="0.75" right="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
